--- a/backend/src/main/resources/templates/annuel/ETAT_CONGES_PAR_PERSONNE.xlsx
+++ b/backend/src/main/resources/templates/annuel/ETAT_CONGES_PAR_PERSONNE.xlsx
@@ -16,7 +16,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00 &quot;Ar&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="22">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -115,8 +115,37 @@
       <color rgb="00595959"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Carlito"/>
+      <color rgb="FF07324A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF07324A"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF07324A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <i val="1"/>
+      <color rgb="FF07324A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FF07324A"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -183,8 +212,32 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF07324A"/>
+        <bgColor rgb="FF07324A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0C4C67"/>
+        <bgColor rgb="FF0C4C67"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1EDF2"/>
+        <bgColor rgb="FFE1EDF2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FA"/>
+        <bgColor rgb="FFF7F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border/>
     <border/>
     <border>
@@ -231,11 +284,43 @@
         <color rgb="00B8CCE4"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -466,6 +551,68 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="17" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="17" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -762,7 +909,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="90" t="inlineStr">
+      <c r="A1" s="116" t="inlineStr">
         <is>
           <t>GALAXAM — ÉTAT DES CONGÉS PAR PERSONNE</t>
         </is>
@@ -786,131 +933,131 @@
       <c r="R1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="91" t="n"/>
-      <c r="B2" s="91" t="n"/>
-      <c r="C2" s="91" t="n"/>
-      <c r="D2" s="91" t="n"/>
-      <c r="E2" s="91" t="n"/>
-      <c r="F2" s="91" t="n"/>
-      <c r="G2" s="91" t="n"/>
-      <c r="H2" s="91" t="n"/>
-      <c r="I2" s="91" t="n"/>
-      <c r="J2" s="91" t="n"/>
-      <c r="K2" s="91" t="n"/>
-      <c r="L2" s="91" t="n"/>
-      <c r="M2" s="91" t="n"/>
-      <c r="N2" s="91" t="n"/>
-      <c r="O2" s="91" t="n"/>
-      <c r="P2" s="91" t="n"/>
-      <c r="Q2" s="91" t="n"/>
-      <c r="R2" s="91" t="n"/>
+      <c r="A2" s="117" t="n"/>
+      <c r="B2" s="117" t="n"/>
+      <c r="C2" s="117" t="n"/>
+      <c r="D2" s="117" t="n"/>
+      <c r="E2" s="117" t="n"/>
+      <c r="F2" s="117" t="n"/>
+      <c r="G2" s="117" t="n"/>
+      <c r="H2" s="117" t="n"/>
+      <c r="I2" s="117" t="n"/>
+      <c r="J2" s="117" t="n"/>
+      <c r="K2" s="117" t="n"/>
+      <c r="L2" s="117" t="n"/>
+      <c r="M2" s="117" t="n"/>
+      <c r="N2" s="117" t="n"/>
+      <c r="O2" s="117" t="n"/>
+      <c r="P2" s="117" t="n"/>
+      <c r="Q2" s="117" t="n"/>
+      <c r="R2" s="117" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="92" t="inlineStr">
+      <c r="A3" s="118" t="inlineStr">
         <is>
           <t>Matricule</t>
         </is>
       </c>
-      <c r="B3" s="93" t="n"/>
-      <c r="C3" s="92" t="inlineStr">
+      <c r="B3" s="119" t="n"/>
+      <c r="C3" s="118" t="inlineStr">
         <is>
           <t>Nom &amp; prénom</t>
         </is>
       </c>
-      <c r="D3" s="93" t="n"/>
-      <c r="E3" s="93" t="n"/>
-      <c r="F3" s="92" t="inlineStr">
+      <c r="D3" s="120" t="n"/>
+      <c r="E3" s="119" t="n"/>
+      <c r="F3" s="118" t="inlineStr">
         <is>
           <t>Filiale</t>
         </is>
       </c>
-      <c r="G3" s="93" t="n"/>
-      <c r="H3" s="92" t="inlineStr">
+      <c r="G3" s="119" t="n"/>
+      <c r="H3" s="118" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="I3" s="93" t="n"/>
-      <c r="J3" s="92" t="inlineStr">
+      <c r="I3" s="119" t="n"/>
+      <c r="J3" s="118" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="K3" s="93" t="n"/>
-      <c r="L3" s="93" t="n"/>
-      <c r="M3" s="92" t="inlineStr">
+      <c r="K3" s="120" t="n"/>
+      <c r="L3" s="119" t="n"/>
+      <c r="M3" s="118" t="inlineStr">
         <is>
           <t>Période de référence</t>
         </is>
       </c>
-      <c r="N3" s="93" t="n"/>
-      <c r="O3" s="93" t="n"/>
-      <c r="P3" s="93" t="n"/>
-      <c r="Q3" s="93" t="n"/>
-      <c r="R3" s="93" t="n"/>
+      <c r="N3" s="120" t="n"/>
+      <c r="O3" s="120" t="n"/>
+      <c r="P3" s="119" t="n"/>
+      <c r="Q3" s="121" t="n"/>
+      <c r="R3" s="121" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="92" t="str"/>
-      <c r="B4" s="93" t="n"/>
-      <c r="C4" s="93" t="n"/>
-      <c r="D4" s="93" t="n"/>
-      <c r="E4" s="93" t="n"/>
-      <c r="F4" s="93" t="n"/>
-      <c r="G4" s="93" t="n"/>
-      <c r="H4" s="93" t="n"/>
-      <c r="I4" s="93" t="n"/>
-      <c r="J4" s="93" t="n"/>
-      <c r="K4" s="93" t="n"/>
-      <c r="L4" s="93" t="n"/>
-      <c r="M4" s="92" t="inlineStr">
+      <c r="A4" s="118" t="str"/>
+      <c r="B4" s="120" t="n"/>
+      <c r="C4" s="120" t="n"/>
+      <c r="D4" s="120" t="n"/>
+      <c r="E4" s="120" t="n"/>
+      <c r="F4" s="120" t="n"/>
+      <c r="G4" s="120" t="n"/>
+      <c r="H4" s="120" t="n"/>
+      <c r="I4" s="120" t="n"/>
+      <c r="J4" s="120" t="n"/>
+      <c r="K4" s="120" t="n"/>
+      <c r="L4" s="119" t="n"/>
+      <c r="M4" s="118" t="inlineStr">
         <is>
           <t>Du</t>
         </is>
       </c>
-      <c r="N4" s="93" t="n"/>
-      <c r="O4" s="92" t="inlineStr">
+      <c r="N4" s="119" t="n"/>
+      <c r="O4" s="118" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="P4" s="93" t="n"/>
-      <c r="Q4" s="93" t="n"/>
-      <c r="R4" s="93" t="n"/>
+      <c r="P4" s="119" t="n"/>
+      <c r="Q4" s="121" t="n"/>
+      <c r="R4" s="121" t="n"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="94" t="inlineStr">
+      <c r="A5" s="122" t="inlineStr">
         <is>
           <t>N° mois</t>
         </is>
       </c>
-      <c r="B5" s="95" t="n"/>
-      <c r="C5" s="21" t="inlineStr">
+      <c r="B5" s="119" t="n"/>
+      <c r="C5" s="123" t="inlineStr">
         <is>
           <t>Valorisation ouverture</t>
         </is>
       </c>
       <c r="D5" s="95" t="n"/>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="123" t="inlineStr">
         <is>
           <t>TCONGE ouverture</t>
         </is>
       </c>
       <c r="F5" s="95" t="n"/>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="123" t="inlineStr">
         <is>
           <t>Mode de reprise</t>
         </is>
       </c>
       <c r="H5" s="95" t="n"/>
       <c r="I5" s="95" t="n"/>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="J5" s="123" t="inlineStr">
         <is>
           <t>Statut période</t>
         </is>
       </c>
       <c r="K5" s="95" t="n"/>
       <c r="L5" s="95" t="n"/>
-      <c r="M5" s="21" t="inlineStr">
+      <c r="M5" s="123" t="inlineStr">
         <is>
           <t>TCONGE clôture</t>
         </is>
@@ -920,107 +1067,107 @@
       <c r="P5" s="95" t="n"/>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="96" t="inlineStr">
+      <c r="A6" s="124" t="inlineStr">
         <is>
           <t>Mois / période paie</t>
         </is>
       </c>
-      <c r="B6" s="96" t="inlineStr">
+      <c r="B6" s="124" t="inlineStr">
         <is>
           <t>Salaire de base (Ar)</t>
         </is>
       </c>
-      <c r="C6" s="97" t="inlineStr">
+      <c r="C6" s="124" t="inlineStr">
         <is>
           <t>Jours base calcul
 (formule)</t>
         </is>
       </c>
-      <c r="D6" s="96" t="inlineStr">
+      <c r="D6" s="124" t="inlineStr">
         <is>
           <t>Absences
 (j)</t>
         </is>
       </c>
-      <c r="E6" s="96" t="inlineStr">
+      <c r="E6" s="124" t="inlineStr">
         <is>
           <t>Retenue
 absence (Ar)</t>
         </is>
       </c>
-      <c r="F6" s="96" t="inlineStr">
+      <c r="F6" s="124" t="inlineStr">
         <is>
           <t>Congés pris
 (j)</t>
         </is>
       </c>
-      <c r="G6" s="96" t="inlineStr">
+      <c r="G6" s="124" t="inlineStr">
         <is>
           <t>TCONGE
 applicable (Ar/j)</t>
         </is>
       </c>
-      <c r="H6" s="96" t="inlineStr">
+      <c r="H6" s="124" t="inlineStr">
         <is>
           <t>Indemnité
 congé (Ar)</t>
         </is>
       </c>
-      <c r="I6" s="96" t="inlineStr">
+      <c r="I6" s="124" t="inlineStr">
         <is>
           <t>HS
 rémunérées (Ar)</t>
         </is>
       </c>
-      <c r="J6" s="97" t="inlineStr">
+      <c r="J6" s="124" t="inlineStr">
         <is>
           <t>Base valo
 (sal+HS) (Ar)</t>
         </is>
       </c>
-      <c r="K6" s="96" t="inlineStr">
+      <c r="K6" s="124" t="inlineStr">
         <is>
           <t>Base activité
 (j)</t>
         </is>
       </c>
-      <c r="L6" s="96" t="inlineStr">
+      <c r="L6" s="124" t="inlineStr">
         <is>
           <t>Droits acquis
 (j)</t>
         </is>
       </c>
-      <c r="M6" s="96" t="inlineStr">
+      <c r="M6" s="124" t="inlineStr">
         <is>
           <t>Valorisation
 acquise (Ar)</t>
         </is>
       </c>
-      <c r="N6" s="96" t="inlineStr">
+      <c r="N6" s="124" t="inlineStr">
         <is>
           <t>Cumul droits
 (j)</t>
         </is>
       </c>
-      <c r="O6" s="96" t="inlineStr">
+      <c r="O6" s="124" t="inlineStr">
         <is>
           <t>Cumul
 valo. (Ar)</t>
         </is>
       </c>
-      <c r="P6" s="96" t="inlineStr">
+      <c r="P6" s="124" t="inlineStr">
         <is>
           <t>Solde dispo.
 (j)</t>
         </is>
       </c>
-      <c r="Q6" s="96" t="inlineStr">
+      <c r="Q6" s="124" t="inlineStr">
         <is>
           <t>Valeur stock
 historisée (Ar)</t>
         </is>
       </c>
-      <c r="R6" s="97" t="inlineStr">
+      <c r="R6" s="124" t="inlineStr">
         <is>
           <t>Solde × TCONGE
 estimation (Ar)</t>
@@ -1028,7 +1175,7 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="98" t="inlineStr">
+      <c r="A7" s="125" t="inlineStr">
         <is>
           <t>Mois / période</t>
         </is>
@@ -1038,7 +1185,7 @@
           <t>Salaire de base</t>
         </is>
       </c>
-      <c r="C7" s="100" t="inlineStr">
+      <c r="C7" s="126" t="inlineStr">
         <is>
           <t>Absence constatée</t>
         </is>
@@ -1109,12 +1256,12 @@
         </is>
       </c>
       <c r="Q7" s="99" t="n"/>
-      <c r="R7" s="100" t="n"/>
+      <c r="R7" s="126" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="98" t="n"/>
+      <c r="A8" s="125" t="n"/>
       <c r="B8" s="101" t="n"/>
-      <c r="C8" s="102" t="n"/>
+      <c r="C8" s="127" t="n"/>
       <c r="D8" s="101" t="n"/>
       <c r="E8" s="103" t="n"/>
       <c r="F8" s="101" t="n"/>
@@ -1129,12 +1276,12 @@
       <c r="O8" s="103" t="n"/>
       <c r="P8" s="101" t="n"/>
       <c r="Q8" s="99" t="n"/>
-      <c r="R8" s="100" t="n"/>
+      <c r="R8" s="126" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="98" t="n"/>
+      <c r="A9" s="125" t="n"/>
       <c r="B9" s="101" t="n"/>
-      <c r="C9" s="102" t="n"/>
+      <c r="C9" s="127" t="n"/>
       <c r="D9" s="101" t="n"/>
       <c r="E9" s="103" t="n"/>
       <c r="F9" s="101" t="n"/>
@@ -1149,12 +1296,12 @@
       <c r="O9" s="103" t="n"/>
       <c r="P9" s="101" t="n"/>
       <c r="Q9" s="99" t="n"/>
-      <c r="R9" s="100" t="n"/>
+      <c r="R9" s="126" t="n"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="98" t="n"/>
+      <c r="A10" s="125" t="n"/>
       <c r="B10" s="101" t="n"/>
-      <c r="C10" s="102" t="n"/>
+      <c r="C10" s="127" t="n"/>
       <c r="D10" s="101" t="n"/>
       <c r="E10" s="103" t="n"/>
       <c r="F10" s="101" t="n"/>
@@ -1169,12 +1316,12 @@
       <c r="O10" s="103" t="n"/>
       <c r="P10" s="101" t="n"/>
       <c r="Q10" s="99" t="n"/>
-      <c r="R10" s="100" t="n"/>
+      <c r="R10" s="126" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="98" t="n"/>
+      <c r="A11" s="125" t="n"/>
       <c r="B11" s="101" t="n"/>
-      <c r="C11" s="102" t="n"/>
+      <c r="C11" s="127" t="n"/>
       <c r="D11" s="101" t="n"/>
       <c r="E11" s="103" t="n"/>
       <c r="F11" s="101" t="n"/>
@@ -1189,12 +1336,12 @@
       <c r="O11" s="103" t="n"/>
       <c r="P11" s="101" t="n"/>
       <c r="Q11" s="99" t="n"/>
-      <c r="R11" s="100" t="n"/>
+      <c r="R11" s="126" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="98" t="n"/>
+      <c r="A12" s="125" t="n"/>
       <c r="B12" s="101" t="n"/>
-      <c r="C12" s="102" t="n"/>
+      <c r="C12" s="127" t="n"/>
       <c r="D12" s="101" t="n"/>
       <c r="E12" s="103" t="n"/>
       <c r="F12" s="101" t="n"/>
@@ -1209,12 +1356,12 @@
       <c r="O12" s="103" t="n"/>
       <c r="P12" s="101" t="n"/>
       <c r="Q12" s="99" t="n"/>
-      <c r="R12" s="100" t="n"/>
+      <c r="R12" s="126" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="98" t="n"/>
+      <c r="A13" s="125" t="n"/>
       <c r="B13" s="101" t="n"/>
-      <c r="C13" s="102" t="n"/>
+      <c r="C13" s="127" t="n"/>
       <c r="D13" s="101" t="n"/>
       <c r="E13" s="103" t="n"/>
       <c r="F13" s="101" t="n"/>
@@ -1229,12 +1376,12 @@
       <c r="O13" s="103" t="n"/>
       <c r="P13" s="101" t="n"/>
       <c r="Q13" s="99" t="n"/>
-      <c r="R13" s="100" t="n"/>
+      <c r="R13" s="126" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="98" t="n"/>
+      <c r="A14" s="125" t="n"/>
       <c r="B14" s="101" t="n"/>
-      <c r="C14" s="102" t="n"/>
+      <c r="C14" s="127" t="n"/>
       <c r="D14" s="101" t="n"/>
       <c r="E14" s="103" t="n"/>
       <c r="F14" s="101" t="n"/>
@@ -1249,12 +1396,12 @@
       <c r="O14" s="103" t="n"/>
       <c r="P14" s="101" t="n"/>
       <c r="Q14" s="99" t="n"/>
-      <c r="R14" s="100" t="n"/>
+      <c r="R14" s="126" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="98" t="n"/>
+      <c r="A15" s="125" t="n"/>
       <c r="B15" s="101" t="n"/>
-      <c r="C15" s="102" t="n"/>
+      <c r="C15" s="127" t="n"/>
       <c r="D15" s="101" t="n"/>
       <c r="E15" s="103" t="n"/>
       <c r="F15" s="101" t="n"/>
@@ -1269,12 +1416,12 @@
       <c r="O15" s="103" t="n"/>
       <c r="P15" s="101" t="n"/>
       <c r="Q15" s="99" t="n"/>
-      <c r="R15" s="100" t="n"/>
+      <c r="R15" s="126" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="98" t="n"/>
+      <c r="A16" s="125" t="n"/>
       <c r="B16" s="101" t="n"/>
-      <c r="C16" s="102" t="n"/>
+      <c r="C16" s="127" t="n"/>
       <c r="D16" s="101" t="n"/>
       <c r="E16" s="103" t="n"/>
       <c r="F16" s="101" t="n"/>
@@ -1289,12 +1436,12 @@
       <c r="O16" s="103" t="n"/>
       <c r="P16" s="101" t="n"/>
       <c r="Q16" s="99" t="n"/>
-      <c r="R16" s="100" t="n"/>
+      <c r="R16" s="126" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="98" t="n"/>
+      <c r="A17" s="125" t="n"/>
       <c r="B17" s="101" t="n"/>
-      <c r="C17" s="102" t="n"/>
+      <c r="C17" s="127" t="n"/>
       <c r="D17" s="101" t="n"/>
       <c r="E17" s="103" t="n"/>
       <c r="F17" s="101" t="n"/>
@@ -1309,12 +1456,12 @@
       <c r="O17" s="103" t="n"/>
       <c r="P17" s="101" t="n"/>
       <c r="Q17" s="99" t="n"/>
-      <c r="R17" s="100" t="n"/>
+      <c r="R17" s="126" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="98" t="n"/>
+      <c r="A18" s="125" t="n"/>
       <c r="B18" s="101" t="n"/>
-      <c r="C18" s="102" t="n"/>
+      <c r="C18" s="127" t="n"/>
       <c r="D18" s="101" t="n"/>
       <c r="E18" s="103" t="n"/>
       <c r="F18" s="101" t="n"/>
@@ -1329,58 +1476,58 @@
       <c r="O18" s="103" t="n"/>
       <c r="P18" s="101" t="n"/>
       <c r="Q18" s="99" t="n"/>
-      <c r="R18" s="100" t="n"/>
+      <c r="R18" s="126" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="104" t="inlineStr">
+      <c r="A19" s="128" t="inlineStr">
         <is>
           <t>TOTAL ENREGISTRÉ / SITUATION</t>
         </is>
       </c>
-      <c r="B19" s="105">
+      <c r="B19" s="129">
         <f>SUM(B7:B18)</f>
         <v/>
       </c>
-      <c r="C19" s="105" t="n"/>
-      <c r="D19" s="105">
+      <c r="C19" s="129" t="n"/>
+      <c r="D19" s="129">
         <f>SUM(D7:D18)</f>
         <v/>
       </c>
-      <c r="E19" s="106">
+      <c r="E19" s="130">
         <f>SUM(E7:E18)</f>
         <v/>
       </c>
-      <c r="F19" s="105">
+      <c r="F19" s="129">
         <f>SUM(F7:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="105" t="n"/>
-      <c r="H19" s="105">
+      <c r="G19" s="129" t="n"/>
+      <c r="H19" s="129">
         <f>SUM(H7:H18)</f>
         <v/>
       </c>
-      <c r="I19" s="105">
+      <c r="I19" s="129">
         <f>SUM(I7:I18)</f>
         <v/>
       </c>
-      <c r="J19" s="106" t="n"/>
-      <c r="K19" s="106">
+      <c r="J19" s="130" t="n"/>
+      <c r="K19" s="130">
         <f>SUM(K7:K18)</f>
         <v/>
       </c>
-      <c r="L19" s="105" t="n"/>
-      <c r="M19" s="106">
+      <c r="L19" s="129" t="n"/>
+      <c r="M19" s="130">
         <f>SUM(M7:M18)</f>
         <v/>
       </c>
-      <c r="N19" s="105">
+      <c r="N19" s="129">
         <f>SUM(N7:N18)</f>
         <v/>
       </c>
-      <c r="O19" s="106" t="n"/>
-      <c r="P19" s="105" t="n"/>
-      <c r="Q19" s="107" t="n"/>
-      <c r="R19" s="107" t="n"/>
+      <c r="O19" s="130" t="n"/>
+      <c r="P19" s="129" t="n"/>
+      <c r="Q19" s="131" t="n"/>
+      <c r="R19" s="131" t="n"/>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="108" t="inlineStr">
@@ -1388,26 +1535,27 @@
           <t>Données enregistrées dans le SIRH à la date de situation. Les colonnes vertes (Jours base calcul, Solde×TCONGE estimation) correspondent aux colonnes 'formule' et 'Solde×taux' de l'OHATRA DAF. La valeur stock historisée (col Q) est calculée par FIFO depuis les lots de droits ; l'estimation simple (col R = Solde × TCONGE) sert au cross-check DAF.</t>
         </is>
       </c>
-      <c r="B20" s="109" t="n"/>
-      <c r="C20" s="109" t="n"/>
-      <c r="D20" s="109" t="n"/>
-      <c r="E20" s="109" t="n"/>
-      <c r="F20" s="109" t="n"/>
-      <c r="G20" s="109" t="n"/>
-      <c r="H20" s="109" t="n"/>
-      <c r="I20" s="109" t="n"/>
-      <c r="J20" s="109" t="n"/>
-      <c r="K20" s="109" t="n"/>
-      <c r="L20" s="109" t="n"/>
-      <c r="M20" s="109" t="n"/>
-      <c r="N20" s="109" t="n"/>
-      <c r="O20" s="109" t="n"/>
-      <c r="P20" s="109" t="n"/>
-      <c r="Q20" s="109" t="n"/>
-      <c r="R20" s="109" t="n"/>
-    </row>
+      <c r="B20" s="120" t="n"/>
+      <c r="C20" s="120" t="n"/>
+      <c r="D20" s="120" t="n"/>
+      <c r="E20" s="120" t="n"/>
+      <c r="F20" s="120" t="n"/>
+      <c r="G20" s="120" t="n"/>
+      <c r="H20" s="120" t="n"/>
+      <c r="I20" s="120" t="n"/>
+      <c r="J20" s="120" t="n"/>
+      <c r="K20" s="120" t="n"/>
+      <c r="L20" s="120" t="n"/>
+      <c r="M20" s="120" t="n"/>
+      <c r="N20" s="120" t="n"/>
+      <c r="O20" s="120" t="n"/>
+      <c r="P20" s="120" t="n"/>
+      <c r="Q20" s="120" t="n"/>
+      <c r="R20" s="119" t="n"/>
+    </row>
+    <row r="21"/>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="53" t="inlineStr">
+      <c r="A22" s="132" t="inlineStr">
         <is>
           <t>Principe : les droits, valorisations, TCONGE et soldes sont calculés/historisés par le SIRH. Cet état les restitue ; seules les totalisations de présentation peuvent être des formules Excel.</t>
         </is>
@@ -1476,7 +1624,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="71" t="inlineStr">
+      <c r="A1" s="133" t="inlineStr">
         <is>
           <t>GALAXAM — HISTORIQUE DES MOUVEMENTS DE CONGÉS</t>
         </is>
@@ -1492,1276 +1640,1276 @@
       <c r="J1" s="1" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="94" t="n"/>
-      <c r="B2" s="94" t="n"/>
-      <c r="C2" s="94" t="n"/>
-      <c r="D2" s="94" t="n"/>
-      <c r="E2" s="94" t="n"/>
-      <c r="F2" s="94" t="n"/>
-      <c r="G2" s="94" t="n"/>
-      <c r="H2" s="94" t="n"/>
-      <c r="I2" s="94" t="inlineStr">
+      <c r="A2" s="122" t="n"/>
+      <c r="B2" s="122" t="n"/>
+      <c r="C2" s="122" t="n"/>
+      <c r="D2" s="122" t="n"/>
+      <c r="E2" s="122" t="n"/>
+      <c r="F2" s="122" t="n"/>
+      <c r="G2" s="122" t="n"/>
+      <c r="H2" s="122" t="n"/>
+      <c r="I2" s="122" t="inlineStr">
         <is>
           <t>Valeur du stock après mvt (Ar)</t>
         </is>
       </c>
-      <c r="J2" s="94" t="inlineStr">
+      <c r="J2" s="122" t="inlineStr">
         <is>
           <t>Origine / provenance</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="134" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="134" t="inlineStr">
         <is>
           <t>Type mouvement</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="134" t="inlineStr">
         <is>
           <t>Référence demande</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
+      <c r="D3" s="134" t="inlineStr">
         <is>
           <t>Libellé / commentaire</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="134" t="inlineStr">
         <is>
           <t>Crédit (j)</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
+      <c r="F3" s="134" t="inlineStr">
         <is>
           <t>Débit (j)</t>
         </is>
       </c>
-      <c r="G3" s="24" t="inlineStr">
+      <c r="G3" s="134" t="inlineStr">
         <is>
           <t>Solde après mouvement (j)</t>
         </is>
       </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="H3" s="134" t="inlineStr">
         <is>
           <t>TCONGE applicable</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="134" t="inlineStr">
         <is>
           <t>Valeur indicative</t>
         </is>
       </c>
-      <c r="J3" s="24" t="inlineStr">
+      <c r="J3" s="134" t="inlineStr">
         <is>
           <t>Origine / provenance</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="32" t="n"/>
-      <c r="B4" s="32" t="n"/>
-      <c r="C4" s="32" t="n"/>
-      <c r="D4" s="32" t="n"/>
-      <c r="E4" s="110" t="n"/>
-      <c r="F4" s="110" t="n"/>
-      <c r="G4" s="110" t="n"/>
-      <c r="H4" s="111" t="n"/>
-      <c r="I4" s="111" t="n"/>
-      <c r="J4" s="32" t="n"/>
+      <c r="A4" s="135" t="n"/>
+      <c r="B4" s="135" t="n"/>
+      <c r="C4" s="135" t="n"/>
+      <c r="D4" s="135" t="n"/>
+      <c r="E4" s="136" t="n"/>
+      <c r="F4" s="136" t="n"/>
+      <c r="G4" s="136" t="n"/>
+      <c r="H4" s="137" t="n"/>
+      <c r="I4" s="137" t="n"/>
+      <c r="J4" s="135" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="n"/>
-      <c r="B5" s="33" t="n"/>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="112" t="n"/>
-      <c r="F5" s="112" t="n"/>
-      <c r="G5" s="112" t="n"/>
-      <c r="H5" s="113" t="n"/>
-      <c r="I5" s="113" t="n"/>
-      <c r="J5" s="33" t="n"/>
+      <c r="A5" s="138" t="n"/>
+      <c r="B5" s="138" t="n"/>
+      <c r="C5" s="138" t="n"/>
+      <c r="D5" s="138" t="n"/>
+      <c r="E5" s="139" t="n"/>
+      <c r="F5" s="139" t="n"/>
+      <c r="G5" s="139" t="n"/>
+      <c r="H5" s="140" t="n"/>
+      <c r="I5" s="140" t="n"/>
+      <c r="J5" s="138" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="32" t="n"/>
-      <c r="B6" s="32" t="n"/>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="32" t="n"/>
-      <c r="E6" s="110" t="n"/>
-      <c r="F6" s="110" t="n"/>
-      <c r="G6" s="110" t="n"/>
-      <c r="H6" s="111" t="n"/>
-      <c r="I6" s="111" t="n"/>
-      <c r="J6" s="32" t="n"/>
+      <c r="A6" s="135" t="n"/>
+      <c r="B6" s="135" t="n"/>
+      <c r="C6" s="135" t="n"/>
+      <c r="D6" s="135" t="n"/>
+      <c r="E6" s="136" t="n"/>
+      <c r="F6" s="136" t="n"/>
+      <c r="G6" s="136" t="n"/>
+      <c r="H6" s="137" t="n"/>
+      <c r="I6" s="137" t="n"/>
+      <c r="J6" s="135" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="33" t="n"/>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="112" t="n"/>
-      <c r="F7" s="112" t="n"/>
-      <c r="G7" s="112" t="n"/>
-      <c r="H7" s="113" t="n"/>
-      <c r="I7" s="113" t="n"/>
-      <c r="J7" s="33" t="n"/>
+      <c r="A7" s="138" t="n"/>
+      <c r="B7" s="138" t="n"/>
+      <c r="C7" s="138" t="n"/>
+      <c r="D7" s="138" t="n"/>
+      <c r="E7" s="139" t="n"/>
+      <c r="F7" s="139" t="n"/>
+      <c r="G7" s="139" t="n"/>
+      <c r="H7" s="140" t="n"/>
+      <c r="I7" s="140" t="n"/>
+      <c r="J7" s="138" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n"/>
-      <c r="B8" s="32" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="110" t="n"/>
-      <c r="F8" s="110" t="n"/>
-      <c r="G8" s="110" t="n"/>
-      <c r="H8" s="111" t="n"/>
-      <c r="I8" s="111" t="n"/>
-      <c r="J8" s="32" t="n"/>
+      <c r="A8" s="135" t="n"/>
+      <c r="B8" s="135" t="n"/>
+      <c r="C8" s="135" t="n"/>
+      <c r="D8" s="135" t="n"/>
+      <c r="E8" s="136" t="n"/>
+      <c r="F8" s="136" t="n"/>
+      <c r="G8" s="136" t="n"/>
+      <c r="H8" s="137" t="n"/>
+      <c r="I8" s="137" t="n"/>
+      <c r="J8" s="135" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="33" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="112" t="n"/>
-      <c r="F9" s="112" t="n"/>
-      <c r="G9" s="112" t="n"/>
-      <c r="H9" s="113" t="n"/>
-      <c r="I9" s="113" t="n"/>
-      <c r="J9" s="33" t="n"/>
+      <c r="A9" s="138" t="n"/>
+      <c r="B9" s="138" t="n"/>
+      <c r="C9" s="138" t="n"/>
+      <c r="D9" s="138" t="n"/>
+      <c r="E9" s="139" t="n"/>
+      <c r="F9" s="139" t="n"/>
+      <c r="G9" s="139" t="n"/>
+      <c r="H9" s="140" t="n"/>
+      <c r="I9" s="140" t="n"/>
+      <c r="J9" s="138" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n"/>
-      <c r="B10" s="32" t="n"/>
-      <c r="C10" s="32" t="n"/>
-      <c r="D10" s="32" t="n"/>
-      <c r="E10" s="110" t="n"/>
-      <c r="F10" s="110" t="n"/>
-      <c r="G10" s="110" t="n"/>
-      <c r="H10" s="111" t="n"/>
-      <c r="I10" s="111" t="n"/>
-      <c r="J10" s="32" t="n"/>
+      <c r="A10" s="135" t="n"/>
+      <c r="B10" s="135" t="n"/>
+      <c r="C10" s="135" t="n"/>
+      <c r="D10" s="135" t="n"/>
+      <c r="E10" s="136" t="n"/>
+      <c r="F10" s="136" t="n"/>
+      <c r="G10" s="136" t="n"/>
+      <c r="H10" s="137" t="n"/>
+      <c r="I10" s="137" t="n"/>
+      <c r="J10" s="135" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="33" t="n"/>
-      <c r="B11" s="33" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="33" t="n"/>
-      <c r="E11" s="112" t="n"/>
-      <c r="F11" s="112" t="n"/>
-      <c r="G11" s="112" t="n"/>
-      <c r="H11" s="113" t="n"/>
-      <c r="I11" s="113" t="n"/>
-      <c r="J11" s="33" t="n"/>
+      <c r="A11" s="138" t="n"/>
+      <c r="B11" s="138" t="n"/>
+      <c r="C11" s="138" t="n"/>
+      <c r="D11" s="138" t="n"/>
+      <c r="E11" s="139" t="n"/>
+      <c r="F11" s="139" t="n"/>
+      <c r="G11" s="139" t="n"/>
+      <c r="H11" s="140" t="n"/>
+      <c r="I11" s="140" t="n"/>
+      <c r="J11" s="138" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="n"/>
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="110" t="n"/>
-      <c r="F12" s="110" t="n"/>
-      <c r="G12" s="110" t="n"/>
-      <c r="H12" s="111" t="n"/>
-      <c r="I12" s="111" t="n"/>
-      <c r="J12" s="32" t="n"/>
+      <c r="A12" s="135" t="n"/>
+      <c r="B12" s="135" t="n"/>
+      <c r="C12" s="135" t="n"/>
+      <c r="D12" s="135" t="n"/>
+      <c r="E12" s="136" t="n"/>
+      <c r="F12" s="136" t="n"/>
+      <c r="G12" s="136" t="n"/>
+      <c r="H12" s="137" t="n"/>
+      <c r="I12" s="137" t="n"/>
+      <c r="J12" s="135" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="33" t="n"/>
-      <c r="B13" s="33" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="112" t="n"/>
-      <c r="F13" s="112" t="n"/>
-      <c r="G13" s="112" t="n"/>
-      <c r="H13" s="113" t="n"/>
-      <c r="I13" s="113" t="n"/>
-      <c r="J13" s="33" t="n"/>
+      <c r="A13" s="138" t="n"/>
+      <c r="B13" s="138" t="n"/>
+      <c r="C13" s="138" t="n"/>
+      <c r="D13" s="138" t="n"/>
+      <c r="E13" s="139" t="n"/>
+      <c r="F13" s="139" t="n"/>
+      <c r="G13" s="139" t="n"/>
+      <c r="H13" s="140" t="n"/>
+      <c r="I13" s="140" t="n"/>
+      <c r="J13" s="138" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="n"/>
-      <c r="B14" s="32" t="n"/>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="110" t="n"/>
-      <c r="F14" s="110" t="n"/>
-      <c r="G14" s="110" t="n"/>
-      <c r="H14" s="111" t="n"/>
-      <c r="I14" s="111" t="n"/>
-      <c r="J14" s="32" t="n"/>
+      <c r="A14" s="135" t="n"/>
+      <c r="B14" s="135" t="n"/>
+      <c r="C14" s="135" t="n"/>
+      <c r="D14" s="135" t="n"/>
+      <c r="E14" s="136" t="n"/>
+      <c r="F14" s="136" t="n"/>
+      <c r="G14" s="136" t="n"/>
+      <c r="H14" s="137" t="n"/>
+      <c r="I14" s="137" t="n"/>
+      <c r="J14" s="135" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="33" t="n"/>
-      <c r="B15" s="33" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="112" t="n"/>
-      <c r="F15" s="112" t="n"/>
-      <c r="G15" s="112" t="n"/>
-      <c r="H15" s="113" t="n"/>
-      <c r="I15" s="113" t="n"/>
-      <c r="J15" s="33" t="n"/>
+      <c r="A15" s="138" t="n"/>
+      <c r="B15" s="138" t="n"/>
+      <c r="C15" s="138" t="n"/>
+      <c r="D15" s="138" t="n"/>
+      <c r="E15" s="139" t="n"/>
+      <c r="F15" s="139" t="n"/>
+      <c r="G15" s="139" t="n"/>
+      <c r="H15" s="140" t="n"/>
+      <c r="I15" s="140" t="n"/>
+      <c r="J15" s="138" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n"/>
-      <c r="B16" s="32" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="110" t="n"/>
-      <c r="F16" s="110" t="n"/>
-      <c r="G16" s="110" t="n"/>
-      <c r="H16" s="111" t="n"/>
-      <c r="I16" s="111" t="n"/>
-      <c r="J16" s="32" t="n"/>
+      <c r="A16" s="135" t="n"/>
+      <c r="B16" s="135" t="n"/>
+      <c r="C16" s="135" t="n"/>
+      <c r="D16" s="135" t="n"/>
+      <c r="E16" s="136" t="n"/>
+      <c r="F16" s="136" t="n"/>
+      <c r="G16" s="136" t="n"/>
+      <c r="H16" s="137" t="n"/>
+      <c r="I16" s="137" t="n"/>
+      <c r="J16" s="135" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="33" t="n"/>
-      <c r="B17" s="33" t="n"/>
-      <c r="C17" s="33" t="n"/>
-      <c r="D17" s="33" t="n"/>
-      <c r="E17" s="112" t="n"/>
-      <c r="F17" s="112" t="n"/>
-      <c r="G17" s="112" t="n"/>
-      <c r="H17" s="113" t="n"/>
-      <c r="I17" s="113" t="n"/>
-      <c r="J17" s="33" t="n"/>
+      <c r="A17" s="138" t="n"/>
+      <c r="B17" s="138" t="n"/>
+      <c r="C17" s="138" t="n"/>
+      <c r="D17" s="138" t="n"/>
+      <c r="E17" s="139" t="n"/>
+      <c r="F17" s="139" t="n"/>
+      <c r="G17" s="139" t="n"/>
+      <c r="H17" s="140" t="n"/>
+      <c r="I17" s="140" t="n"/>
+      <c r="J17" s="138" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="n"/>
-      <c r="B18" s="32" t="n"/>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="110" t="n"/>
-      <c r="F18" s="110" t="n"/>
-      <c r="G18" s="110" t="n"/>
-      <c r="H18" s="111" t="n"/>
-      <c r="I18" s="111" t="n"/>
-      <c r="J18" s="32" t="n"/>
+      <c r="A18" s="135" t="n"/>
+      <c r="B18" s="135" t="n"/>
+      <c r="C18" s="135" t="n"/>
+      <c r="D18" s="135" t="n"/>
+      <c r="E18" s="136" t="n"/>
+      <c r="F18" s="136" t="n"/>
+      <c r="G18" s="136" t="n"/>
+      <c r="H18" s="137" t="n"/>
+      <c r="I18" s="137" t="n"/>
+      <c r="J18" s="135" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="n"/>
-      <c r="B19" s="33" t="n"/>
-      <c r="C19" s="33" t="n"/>
-      <c r="D19" s="33" t="n"/>
-      <c r="E19" s="112" t="n"/>
-      <c r="F19" s="112" t="n"/>
-      <c r="G19" s="112" t="n"/>
-      <c r="H19" s="113" t="n"/>
-      <c r="I19" s="113" t="n"/>
-      <c r="J19" s="33" t="n"/>
+      <c r="A19" s="138" t="n"/>
+      <c r="B19" s="138" t="n"/>
+      <c r="C19" s="138" t="n"/>
+      <c r="D19" s="138" t="n"/>
+      <c r="E19" s="139" t="n"/>
+      <c r="F19" s="139" t="n"/>
+      <c r="G19" s="139" t="n"/>
+      <c r="H19" s="140" t="n"/>
+      <c r="I19" s="140" t="n"/>
+      <c r="J19" s="138" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n"/>
-      <c r="B20" s="32" t="n"/>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="110" t="n"/>
-      <c r="F20" s="110" t="n"/>
-      <c r="G20" s="110" t="n"/>
-      <c r="H20" s="111" t="n"/>
-      <c r="I20" s="111" t="n"/>
-      <c r="J20" s="32" t="n"/>
+      <c r="A20" s="135" t="n"/>
+      <c r="B20" s="135" t="n"/>
+      <c r="C20" s="135" t="n"/>
+      <c r="D20" s="135" t="n"/>
+      <c r="E20" s="136" t="n"/>
+      <c r="F20" s="136" t="n"/>
+      <c r="G20" s="136" t="n"/>
+      <c r="H20" s="137" t="n"/>
+      <c r="I20" s="137" t="n"/>
+      <c r="J20" s="135" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="n"/>
-      <c r="B21" s="33" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="112" t="n"/>
-      <c r="F21" s="112" t="n"/>
-      <c r="G21" s="112" t="n"/>
-      <c r="H21" s="113" t="n"/>
-      <c r="I21" s="113" t="n"/>
-      <c r="J21" s="33" t="n"/>
+      <c r="A21" s="138" t="n"/>
+      <c r="B21" s="138" t="n"/>
+      <c r="C21" s="138" t="n"/>
+      <c r="D21" s="138" t="n"/>
+      <c r="E21" s="139" t="n"/>
+      <c r="F21" s="139" t="n"/>
+      <c r="G21" s="139" t="n"/>
+      <c r="H21" s="140" t="n"/>
+      <c r="I21" s="140" t="n"/>
+      <c r="J21" s="138" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n"/>
-      <c r="B22" s="32" t="n"/>
-      <c r="C22" s="32" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="110" t="n"/>
-      <c r="F22" s="110" t="n"/>
-      <c r="G22" s="110" t="n"/>
-      <c r="H22" s="111" t="n"/>
-      <c r="I22" s="111" t="n"/>
-      <c r="J22" s="32" t="n"/>
+      <c r="A22" s="135" t="n"/>
+      <c r="B22" s="135" t="n"/>
+      <c r="C22" s="135" t="n"/>
+      <c r="D22" s="135" t="n"/>
+      <c r="E22" s="136" t="n"/>
+      <c r="F22" s="136" t="n"/>
+      <c r="G22" s="136" t="n"/>
+      <c r="H22" s="137" t="n"/>
+      <c r="I22" s="137" t="n"/>
+      <c r="J22" s="135" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="n"/>
-      <c r="B23" s="33" t="n"/>
-      <c r="C23" s="33" t="n"/>
-      <c r="D23" s="33" t="n"/>
-      <c r="E23" s="112" t="n"/>
-      <c r="F23" s="112" t="n"/>
-      <c r="G23" s="112" t="n"/>
-      <c r="H23" s="113" t="n"/>
-      <c r="I23" s="113" t="n"/>
-      <c r="J23" s="33" t="n"/>
+      <c r="A23" s="138" t="n"/>
+      <c r="B23" s="138" t="n"/>
+      <c r="C23" s="138" t="n"/>
+      <c r="D23" s="138" t="n"/>
+      <c r="E23" s="139" t="n"/>
+      <c r="F23" s="139" t="n"/>
+      <c r="G23" s="139" t="n"/>
+      <c r="H23" s="140" t="n"/>
+      <c r="I23" s="140" t="n"/>
+      <c r="J23" s="138" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n"/>
-      <c r="B24" s="32" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="110" t="n"/>
-      <c r="F24" s="110" t="n"/>
-      <c r="G24" s="110" t="n"/>
-      <c r="H24" s="111" t="n"/>
-      <c r="I24" s="111" t="n"/>
-      <c r="J24" s="32" t="n"/>
+      <c r="A24" s="135" t="n"/>
+      <c r="B24" s="135" t="n"/>
+      <c r="C24" s="135" t="n"/>
+      <c r="D24" s="135" t="n"/>
+      <c r="E24" s="136" t="n"/>
+      <c r="F24" s="136" t="n"/>
+      <c r="G24" s="136" t="n"/>
+      <c r="H24" s="137" t="n"/>
+      <c r="I24" s="137" t="n"/>
+      <c r="J24" s="135" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="n"/>
-      <c r="B25" s="33" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="112" t="n"/>
-      <c r="F25" s="112" t="n"/>
-      <c r="G25" s="112" t="n"/>
-      <c r="H25" s="113" t="n"/>
-      <c r="I25" s="113" t="n"/>
-      <c r="J25" s="33" t="n"/>
+      <c r="A25" s="138" t="n"/>
+      <c r="B25" s="138" t="n"/>
+      <c r="C25" s="138" t="n"/>
+      <c r="D25" s="138" t="n"/>
+      <c r="E25" s="139" t="n"/>
+      <c r="F25" s="139" t="n"/>
+      <c r="G25" s="139" t="n"/>
+      <c r="H25" s="140" t="n"/>
+      <c r="I25" s="140" t="n"/>
+      <c r="J25" s="138" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="n"/>
-      <c r="B26" s="32" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="110" t="n"/>
-      <c r="F26" s="110" t="n"/>
-      <c r="G26" s="110" t="n"/>
-      <c r="H26" s="111" t="n"/>
-      <c r="I26" s="111" t="n"/>
-      <c r="J26" s="32" t="n"/>
+      <c r="A26" s="135" t="n"/>
+      <c r="B26" s="135" t="n"/>
+      <c r="C26" s="135" t="n"/>
+      <c r="D26" s="135" t="n"/>
+      <c r="E26" s="136" t="n"/>
+      <c r="F26" s="136" t="n"/>
+      <c r="G26" s="136" t="n"/>
+      <c r="H26" s="137" t="n"/>
+      <c r="I26" s="137" t="n"/>
+      <c r="J26" s="135" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="n"/>
-      <c r="B27" s="33" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="112" t="n"/>
-      <c r="F27" s="112" t="n"/>
-      <c r="G27" s="112" t="n"/>
-      <c r="H27" s="113" t="n"/>
-      <c r="I27" s="113" t="n"/>
-      <c r="J27" s="33" t="n"/>
+      <c r="A27" s="138" t="n"/>
+      <c r="B27" s="138" t="n"/>
+      <c r="C27" s="138" t="n"/>
+      <c r="D27" s="138" t="n"/>
+      <c r="E27" s="139" t="n"/>
+      <c r="F27" s="139" t="n"/>
+      <c r="G27" s="139" t="n"/>
+      <c r="H27" s="140" t="n"/>
+      <c r="I27" s="140" t="n"/>
+      <c r="J27" s="138" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="n"/>
-      <c r="B28" s="32" t="n"/>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="32" t="n"/>
-      <c r="E28" s="110" t="n"/>
-      <c r="F28" s="110" t="n"/>
-      <c r="G28" s="110" t="n"/>
-      <c r="H28" s="111" t="n"/>
-      <c r="I28" s="111" t="n"/>
-      <c r="J28" s="32" t="n"/>
+      <c r="A28" s="135" t="n"/>
+      <c r="B28" s="135" t="n"/>
+      <c r="C28" s="135" t="n"/>
+      <c r="D28" s="135" t="n"/>
+      <c r="E28" s="136" t="n"/>
+      <c r="F28" s="136" t="n"/>
+      <c r="G28" s="136" t="n"/>
+      <c r="H28" s="137" t="n"/>
+      <c r="I28" s="137" t="n"/>
+      <c r="J28" s="135" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="n"/>
-      <c r="B29" s="33" t="n"/>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="33" t="n"/>
-      <c r="E29" s="112" t="n"/>
-      <c r="F29" s="112" t="n"/>
-      <c r="G29" s="112" t="n"/>
-      <c r="H29" s="113" t="n"/>
-      <c r="I29" s="113" t="n"/>
-      <c r="J29" s="33" t="n"/>
+      <c r="A29" s="138" t="n"/>
+      <c r="B29" s="138" t="n"/>
+      <c r="C29" s="138" t="n"/>
+      <c r="D29" s="138" t="n"/>
+      <c r="E29" s="139" t="n"/>
+      <c r="F29" s="139" t="n"/>
+      <c r="G29" s="139" t="n"/>
+      <c r="H29" s="140" t="n"/>
+      <c r="I29" s="140" t="n"/>
+      <c r="J29" s="138" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="n"/>
-      <c r="B30" s="32" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="110" t="n"/>
-      <c r="F30" s="110" t="n"/>
-      <c r="G30" s="110" t="n"/>
-      <c r="H30" s="111" t="n"/>
-      <c r="I30" s="111" t="n"/>
-      <c r="J30" s="32" t="n"/>
+      <c r="A30" s="135" t="n"/>
+      <c r="B30" s="135" t="n"/>
+      <c r="C30" s="135" t="n"/>
+      <c r="D30" s="135" t="n"/>
+      <c r="E30" s="136" t="n"/>
+      <c r="F30" s="136" t="n"/>
+      <c r="G30" s="136" t="n"/>
+      <c r="H30" s="137" t="n"/>
+      <c r="I30" s="137" t="n"/>
+      <c r="J30" s="135" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="n"/>
-      <c r="B31" s="33" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
-      <c r="E31" s="112" t="n"/>
-      <c r="F31" s="112" t="n"/>
-      <c r="G31" s="112" t="n"/>
-      <c r="H31" s="113" t="n"/>
-      <c r="I31" s="113" t="n"/>
-      <c r="J31" s="33" t="n"/>
+      <c r="A31" s="138" t="n"/>
+      <c r="B31" s="138" t="n"/>
+      <c r="C31" s="138" t="n"/>
+      <c r="D31" s="138" t="n"/>
+      <c r="E31" s="139" t="n"/>
+      <c r="F31" s="139" t="n"/>
+      <c r="G31" s="139" t="n"/>
+      <c r="H31" s="140" t="n"/>
+      <c r="I31" s="140" t="n"/>
+      <c r="J31" s="138" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="n"/>
-      <c r="B32" s="32" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="32" t="n"/>
-      <c r="E32" s="110" t="n"/>
-      <c r="F32" s="110" t="n"/>
-      <c r="G32" s="110" t="n"/>
-      <c r="H32" s="111" t="n"/>
-      <c r="I32" s="111" t="n"/>
-      <c r="J32" s="32" t="n"/>
+      <c r="A32" s="135" t="n"/>
+      <c r="B32" s="135" t="n"/>
+      <c r="C32" s="135" t="n"/>
+      <c r="D32" s="135" t="n"/>
+      <c r="E32" s="136" t="n"/>
+      <c r="F32" s="136" t="n"/>
+      <c r="G32" s="136" t="n"/>
+      <c r="H32" s="137" t="n"/>
+      <c r="I32" s="137" t="n"/>
+      <c r="J32" s="135" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="n"/>
-      <c r="B33" s="33" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="112" t="n"/>
-      <c r="F33" s="112" t="n"/>
-      <c r="G33" s="112" t="n"/>
-      <c r="H33" s="113" t="n"/>
-      <c r="I33" s="113" t="n"/>
-      <c r="J33" s="33" t="n"/>
+      <c r="A33" s="138" t="n"/>
+      <c r="B33" s="138" t="n"/>
+      <c r="C33" s="138" t="n"/>
+      <c r="D33" s="138" t="n"/>
+      <c r="E33" s="139" t="n"/>
+      <c r="F33" s="139" t="n"/>
+      <c r="G33" s="139" t="n"/>
+      <c r="H33" s="140" t="n"/>
+      <c r="I33" s="140" t="n"/>
+      <c r="J33" s="138" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="n"/>
-      <c r="B34" s="32" t="n"/>
-      <c r="C34" s="32" t="n"/>
-      <c r="D34" s="32" t="n"/>
-      <c r="E34" s="110" t="n"/>
-      <c r="F34" s="110" t="n"/>
-      <c r="G34" s="110" t="n"/>
-      <c r="H34" s="111" t="n"/>
-      <c r="I34" s="111" t="n"/>
-      <c r="J34" s="32" t="n"/>
+      <c r="A34" s="135" t="n"/>
+      <c r="B34" s="135" t="n"/>
+      <c r="C34" s="135" t="n"/>
+      <c r="D34" s="135" t="n"/>
+      <c r="E34" s="136" t="n"/>
+      <c r="F34" s="136" t="n"/>
+      <c r="G34" s="136" t="n"/>
+      <c r="H34" s="137" t="n"/>
+      <c r="I34" s="137" t="n"/>
+      <c r="J34" s="135" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="n"/>
-      <c r="B35" s="33" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="33" t="n"/>
-      <c r="E35" s="112" t="n"/>
-      <c r="F35" s="112" t="n"/>
-      <c r="G35" s="112" t="n"/>
-      <c r="H35" s="113" t="n"/>
-      <c r="I35" s="113" t="n"/>
-      <c r="J35" s="33" t="n"/>
+      <c r="A35" s="138" t="n"/>
+      <c r="B35" s="138" t="n"/>
+      <c r="C35" s="138" t="n"/>
+      <c r="D35" s="138" t="n"/>
+      <c r="E35" s="139" t="n"/>
+      <c r="F35" s="139" t="n"/>
+      <c r="G35" s="139" t="n"/>
+      <c r="H35" s="140" t="n"/>
+      <c r="I35" s="140" t="n"/>
+      <c r="J35" s="138" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="n"/>
-      <c r="B36" s="32" t="n"/>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="110" t="n"/>
-      <c r="F36" s="110" t="n"/>
-      <c r="G36" s="110" t="n"/>
-      <c r="H36" s="111" t="n"/>
-      <c r="I36" s="111" t="n"/>
-      <c r="J36" s="32" t="n"/>
+      <c r="A36" s="135" t="n"/>
+      <c r="B36" s="135" t="n"/>
+      <c r="C36" s="135" t="n"/>
+      <c r="D36" s="135" t="n"/>
+      <c r="E36" s="136" t="n"/>
+      <c r="F36" s="136" t="n"/>
+      <c r="G36" s="136" t="n"/>
+      <c r="H36" s="137" t="n"/>
+      <c r="I36" s="137" t="n"/>
+      <c r="J36" s="135" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="n"/>
-      <c r="B37" s="33" t="n"/>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="112" t="n"/>
-      <c r="F37" s="112" t="n"/>
-      <c r="G37" s="112" t="n"/>
-      <c r="H37" s="113" t="n"/>
-      <c r="I37" s="113" t="n"/>
-      <c r="J37" s="33" t="n"/>
+      <c r="A37" s="138" t="n"/>
+      <c r="B37" s="138" t="n"/>
+      <c r="C37" s="138" t="n"/>
+      <c r="D37" s="138" t="n"/>
+      <c r="E37" s="139" t="n"/>
+      <c r="F37" s="139" t="n"/>
+      <c r="G37" s="139" t="n"/>
+      <c r="H37" s="140" t="n"/>
+      <c r="I37" s="140" t="n"/>
+      <c r="J37" s="138" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="n"/>
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="32" t="n"/>
-      <c r="D38" s="32" t="n"/>
-      <c r="E38" s="110" t="n"/>
-      <c r="F38" s="110" t="n"/>
-      <c r="G38" s="110" t="n"/>
-      <c r="H38" s="111" t="n"/>
-      <c r="I38" s="111" t="n"/>
-      <c r="J38" s="32" t="n"/>
+      <c r="A38" s="135" t="n"/>
+      <c r="B38" s="135" t="n"/>
+      <c r="C38" s="135" t="n"/>
+      <c r="D38" s="135" t="n"/>
+      <c r="E38" s="136" t="n"/>
+      <c r="F38" s="136" t="n"/>
+      <c r="G38" s="136" t="n"/>
+      <c r="H38" s="137" t="n"/>
+      <c r="I38" s="137" t="n"/>
+      <c r="J38" s="135" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="33" t="n"/>
-      <c r="B39" s="33" t="n"/>
-      <c r="C39" s="33" t="n"/>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="112" t="n"/>
-      <c r="F39" s="112" t="n"/>
-      <c r="G39" s="112" t="n"/>
-      <c r="H39" s="113" t="n"/>
-      <c r="I39" s="113" t="n"/>
-      <c r="J39" s="33" t="n"/>
+      <c r="A39" s="138" t="n"/>
+      <c r="B39" s="138" t="n"/>
+      <c r="C39" s="138" t="n"/>
+      <c r="D39" s="138" t="n"/>
+      <c r="E39" s="139" t="n"/>
+      <c r="F39" s="139" t="n"/>
+      <c r="G39" s="139" t="n"/>
+      <c r="H39" s="140" t="n"/>
+      <c r="I39" s="140" t="n"/>
+      <c r="J39" s="138" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="n"/>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="32" t="n"/>
-      <c r="E40" s="110" t="n"/>
-      <c r="F40" s="110" t="n"/>
-      <c r="G40" s="110" t="n"/>
-      <c r="H40" s="111" t="n"/>
-      <c r="I40" s="111" t="n"/>
-      <c r="J40" s="32" t="n"/>
+      <c r="A40" s="135" t="n"/>
+      <c r="B40" s="135" t="n"/>
+      <c r="C40" s="135" t="n"/>
+      <c r="D40" s="135" t="n"/>
+      <c r="E40" s="136" t="n"/>
+      <c r="F40" s="136" t="n"/>
+      <c r="G40" s="136" t="n"/>
+      <c r="H40" s="137" t="n"/>
+      <c r="I40" s="137" t="n"/>
+      <c r="J40" s="135" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="n"/>
-      <c r="B41" s="33" t="n"/>
-      <c r="C41" s="33" t="n"/>
-      <c r="D41" s="33" t="n"/>
-      <c r="E41" s="112" t="n"/>
-      <c r="F41" s="112" t="n"/>
-      <c r="G41" s="112" t="n"/>
-      <c r="H41" s="113" t="n"/>
-      <c r="I41" s="113" t="n"/>
-      <c r="J41" s="33" t="n"/>
+      <c r="A41" s="138" t="n"/>
+      <c r="B41" s="138" t="n"/>
+      <c r="C41" s="138" t="n"/>
+      <c r="D41" s="138" t="n"/>
+      <c r="E41" s="139" t="n"/>
+      <c r="F41" s="139" t="n"/>
+      <c r="G41" s="139" t="n"/>
+      <c r="H41" s="140" t="n"/>
+      <c r="I41" s="140" t="n"/>
+      <c r="J41" s="138" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="n"/>
-      <c r="B42" s="32" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="D42" s="32" t="n"/>
-      <c r="E42" s="110" t="n"/>
-      <c r="F42" s="110" t="n"/>
-      <c r="G42" s="110" t="n"/>
-      <c r="H42" s="111" t="n"/>
-      <c r="I42" s="111" t="n"/>
-      <c r="J42" s="32" t="n"/>
+      <c r="A42" s="135" t="n"/>
+      <c r="B42" s="135" t="n"/>
+      <c r="C42" s="135" t="n"/>
+      <c r="D42" s="135" t="n"/>
+      <c r="E42" s="136" t="n"/>
+      <c r="F42" s="136" t="n"/>
+      <c r="G42" s="136" t="n"/>
+      <c r="H42" s="137" t="n"/>
+      <c r="I42" s="137" t="n"/>
+      <c r="J42" s="135" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="n"/>
-      <c r="B43" s="33" t="n"/>
-      <c r="C43" s="33" t="n"/>
-      <c r="D43" s="33" t="n"/>
-      <c r="E43" s="112" t="n"/>
-      <c r="F43" s="112" t="n"/>
-      <c r="G43" s="112" t="n"/>
-      <c r="H43" s="113" t="n"/>
-      <c r="I43" s="113" t="n"/>
-      <c r="J43" s="33" t="n"/>
+      <c r="A43" s="138" t="n"/>
+      <c r="B43" s="138" t="n"/>
+      <c r="C43" s="138" t="n"/>
+      <c r="D43" s="138" t="n"/>
+      <c r="E43" s="139" t="n"/>
+      <c r="F43" s="139" t="n"/>
+      <c r="G43" s="139" t="n"/>
+      <c r="H43" s="140" t="n"/>
+      <c r="I43" s="140" t="n"/>
+      <c r="J43" s="138" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="n"/>
-      <c r="B44" s="32" t="n"/>
-      <c r="C44" s="32" t="n"/>
-      <c r="D44" s="32" t="n"/>
-      <c r="E44" s="110" t="n"/>
-      <c r="F44" s="110" t="n"/>
-      <c r="G44" s="110" t="n"/>
-      <c r="H44" s="111" t="n"/>
-      <c r="I44" s="111" t="n"/>
-      <c r="J44" s="32" t="n"/>
+      <c r="A44" s="135" t="n"/>
+      <c r="B44" s="135" t="n"/>
+      <c r="C44" s="135" t="n"/>
+      <c r="D44" s="135" t="n"/>
+      <c r="E44" s="136" t="n"/>
+      <c r="F44" s="136" t="n"/>
+      <c r="G44" s="136" t="n"/>
+      <c r="H44" s="137" t="n"/>
+      <c r="I44" s="137" t="n"/>
+      <c r="J44" s="135" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="33" t="n"/>
-      <c r="B45" s="33" t="n"/>
-      <c r="C45" s="33" t="n"/>
-      <c r="D45" s="33" t="n"/>
-      <c r="E45" s="112" t="n"/>
-      <c r="F45" s="112" t="n"/>
-      <c r="G45" s="112" t="n"/>
-      <c r="H45" s="113" t="n"/>
-      <c r="I45" s="113" t="n"/>
-      <c r="J45" s="33" t="n"/>
+      <c r="A45" s="138" t="n"/>
+      <c r="B45" s="138" t="n"/>
+      <c r="C45" s="138" t="n"/>
+      <c r="D45" s="138" t="n"/>
+      <c r="E45" s="139" t="n"/>
+      <c r="F45" s="139" t="n"/>
+      <c r="G45" s="139" t="n"/>
+      <c r="H45" s="140" t="n"/>
+      <c r="I45" s="140" t="n"/>
+      <c r="J45" s="138" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="n"/>
-      <c r="B46" s="32" t="n"/>
-      <c r="C46" s="32" t="n"/>
-      <c r="D46" s="32" t="n"/>
-      <c r="E46" s="110" t="n"/>
-      <c r="F46" s="110" t="n"/>
-      <c r="G46" s="110" t="n"/>
-      <c r="H46" s="111" t="n"/>
-      <c r="I46" s="111" t="n"/>
-      <c r="J46" s="32" t="n"/>
+      <c r="A46" s="135" t="n"/>
+      <c r="B46" s="135" t="n"/>
+      <c r="C46" s="135" t="n"/>
+      <c r="D46" s="135" t="n"/>
+      <c r="E46" s="136" t="n"/>
+      <c r="F46" s="136" t="n"/>
+      <c r="G46" s="136" t="n"/>
+      <c r="H46" s="137" t="n"/>
+      <c r="I46" s="137" t="n"/>
+      <c r="J46" s="135" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="33" t="n"/>
-      <c r="B47" s="33" t="n"/>
-      <c r="C47" s="33" t="n"/>
-      <c r="D47" s="33" t="n"/>
-      <c r="E47" s="112" t="n"/>
-      <c r="F47" s="112" t="n"/>
-      <c r="G47" s="112" t="n"/>
-      <c r="H47" s="113" t="n"/>
-      <c r="I47" s="113" t="n"/>
-      <c r="J47" s="33" t="n"/>
+      <c r="A47" s="138" t="n"/>
+      <c r="B47" s="138" t="n"/>
+      <c r="C47" s="138" t="n"/>
+      <c r="D47" s="138" t="n"/>
+      <c r="E47" s="139" t="n"/>
+      <c r="F47" s="139" t="n"/>
+      <c r="G47" s="139" t="n"/>
+      <c r="H47" s="140" t="n"/>
+      <c r="I47" s="140" t="n"/>
+      <c r="J47" s="138" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="n"/>
-      <c r="B48" s="32" t="n"/>
-      <c r="C48" s="32" t="n"/>
-      <c r="D48" s="32" t="n"/>
-      <c r="E48" s="110" t="n"/>
-      <c r="F48" s="110" t="n"/>
-      <c r="G48" s="110" t="n"/>
-      <c r="H48" s="111" t="n"/>
-      <c r="I48" s="111" t="n"/>
-      <c r="J48" s="32" t="n"/>
+      <c r="A48" s="135" t="n"/>
+      <c r="B48" s="135" t="n"/>
+      <c r="C48" s="135" t="n"/>
+      <c r="D48" s="135" t="n"/>
+      <c r="E48" s="136" t="n"/>
+      <c r="F48" s="136" t="n"/>
+      <c r="G48" s="136" t="n"/>
+      <c r="H48" s="137" t="n"/>
+      <c r="I48" s="137" t="n"/>
+      <c r="J48" s="135" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="33" t="n"/>
-      <c r="B49" s="33" t="n"/>
-      <c r="C49" s="33" t="n"/>
-      <c r="D49" s="33" t="n"/>
-      <c r="E49" s="112" t="n"/>
-      <c r="F49" s="112" t="n"/>
-      <c r="G49" s="112" t="n"/>
-      <c r="H49" s="113" t="n"/>
-      <c r="I49" s="113" t="n"/>
-      <c r="J49" s="33" t="n"/>
+      <c r="A49" s="138" t="n"/>
+      <c r="B49" s="138" t="n"/>
+      <c r="C49" s="138" t="n"/>
+      <c r="D49" s="138" t="n"/>
+      <c r="E49" s="139" t="n"/>
+      <c r="F49" s="139" t="n"/>
+      <c r="G49" s="139" t="n"/>
+      <c r="H49" s="140" t="n"/>
+      <c r="I49" s="140" t="n"/>
+      <c r="J49" s="138" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="n"/>
-      <c r="B50" s="32" t="n"/>
-      <c r="C50" s="32" t="n"/>
-      <c r="D50" s="32" t="n"/>
-      <c r="E50" s="110" t="n"/>
-      <c r="F50" s="110" t="n"/>
-      <c r="G50" s="110" t="n"/>
-      <c r="H50" s="111" t="n"/>
-      <c r="I50" s="111" t="n"/>
-      <c r="J50" s="32" t="n"/>
+      <c r="A50" s="135" t="n"/>
+      <c r="B50" s="135" t="n"/>
+      <c r="C50" s="135" t="n"/>
+      <c r="D50" s="135" t="n"/>
+      <c r="E50" s="136" t="n"/>
+      <c r="F50" s="136" t="n"/>
+      <c r="G50" s="136" t="n"/>
+      <c r="H50" s="137" t="n"/>
+      <c r="I50" s="137" t="n"/>
+      <c r="J50" s="135" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="n"/>
-      <c r="B51" s="33" t="n"/>
-      <c r="C51" s="33" t="n"/>
-      <c r="D51" s="33" t="n"/>
-      <c r="E51" s="112" t="n"/>
-      <c r="F51" s="112" t="n"/>
-      <c r="G51" s="112" t="n"/>
-      <c r="H51" s="113" t="n"/>
-      <c r="I51" s="113" t="n"/>
-      <c r="J51" s="33" t="n"/>
+      <c r="A51" s="138" t="n"/>
+      <c r="B51" s="138" t="n"/>
+      <c r="C51" s="138" t="n"/>
+      <c r="D51" s="138" t="n"/>
+      <c r="E51" s="139" t="n"/>
+      <c r="F51" s="139" t="n"/>
+      <c r="G51" s="139" t="n"/>
+      <c r="H51" s="140" t="n"/>
+      <c r="I51" s="140" t="n"/>
+      <c r="J51" s="138" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="n"/>
-      <c r="B52" s="32" t="n"/>
-      <c r="C52" s="32" t="n"/>
-      <c r="D52" s="32" t="n"/>
-      <c r="E52" s="110" t="n"/>
-      <c r="F52" s="110" t="n"/>
-      <c r="G52" s="110" t="n"/>
-      <c r="H52" s="111" t="n"/>
-      <c r="I52" s="111" t="n"/>
-      <c r="J52" s="32" t="n"/>
+      <c r="A52" s="135" t="n"/>
+      <c r="B52" s="135" t="n"/>
+      <c r="C52" s="135" t="n"/>
+      <c r="D52" s="135" t="n"/>
+      <c r="E52" s="136" t="n"/>
+      <c r="F52" s="136" t="n"/>
+      <c r="G52" s="136" t="n"/>
+      <c r="H52" s="137" t="n"/>
+      <c r="I52" s="137" t="n"/>
+      <c r="J52" s="135" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="33" t="n"/>
-      <c r="B53" s="33" t="n"/>
-      <c r="C53" s="33" t="n"/>
-      <c r="D53" s="33" t="n"/>
-      <c r="E53" s="112" t="n"/>
-      <c r="F53" s="112" t="n"/>
-      <c r="G53" s="112" t="n"/>
-      <c r="H53" s="113" t="n"/>
-      <c r="I53" s="113" t="n"/>
-      <c r="J53" s="33" t="n"/>
+      <c r="A53" s="138" t="n"/>
+      <c r="B53" s="138" t="n"/>
+      <c r="C53" s="138" t="n"/>
+      <c r="D53" s="138" t="n"/>
+      <c r="E53" s="139" t="n"/>
+      <c r="F53" s="139" t="n"/>
+      <c r="G53" s="139" t="n"/>
+      <c r="H53" s="140" t="n"/>
+      <c r="I53" s="140" t="n"/>
+      <c r="J53" s="138" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="n"/>
-      <c r="B54" s="32" t="n"/>
-      <c r="C54" s="32" t="n"/>
-      <c r="D54" s="32" t="n"/>
-      <c r="E54" s="110" t="n"/>
-      <c r="F54" s="110" t="n"/>
-      <c r="G54" s="110" t="n"/>
-      <c r="H54" s="111" t="n"/>
-      <c r="I54" s="111" t="n"/>
-      <c r="J54" s="32" t="n"/>
+      <c r="A54" s="135" t="n"/>
+      <c r="B54" s="135" t="n"/>
+      <c r="C54" s="135" t="n"/>
+      <c r="D54" s="135" t="n"/>
+      <c r="E54" s="136" t="n"/>
+      <c r="F54" s="136" t="n"/>
+      <c r="G54" s="136" t="n"/>
+      <c r="H54" s="137" t="n"/>
+      <c r="I54" s="137" t="n"/>
+      <c r="J54" s="135" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="33" t="n"/>
-      <c r="B55" s="33" t="n"/>
-      <c r="C55" s="33" t="n"/>
-      <c r="D55" s="33" t="n"/>
-      <c r="E55" s="112" t="n"/>
-      <c r="F55" s="112" t="n"/>
-      <c r="G55" s="112" t="n"/>
-      <c r="H55" s="113" t="n"/>
-      <c r="I55" s="113" t="n"/>
-      <c r="J55" s="33" t="n"/>
+      <c r="A55" s="138" t="n"/>
+      <c r="B55" s="138" t="n"/>
+      <c r="C55" s="138" t="n"/>
+      <c r="D55" s="138" t="n"/>
+      <c r="E55" s="139" t="n"/>
+      <c r="F55" s="139" t="n"/>
+      <c r="G55" s="139" t="n"/>
+      <c r="H55" s="140" t="n"/>
+      <c r="I55" s="140" t="n"/>
+      <c r="J55" s="138" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="n"/>
-      <c r="B56" s="32" t="n"/>
-      <c r="C56" s="32" t="n"/>
-      <c r="D56" s="32" t="n"/>
-      <c r="E56" s="110" t="n"/>
-      <c r="F56" s="110" t="n"/>
-      <c r="G56" s="110" t="n"/>
-      <c r="H56" s="111" t="n"/>
-      <c r="I56" s="111" t="n"/>
-      <c r="J56" s="32" t="n"/>
+      <c r="A56" s="135" t="n"/>
+      <c r="B56" s="135" t="n"/>
+      <c r="C56" s="135" t="n"/>
+      <c r="D56" s="135" t="n"/>
+      <c r="E56" s="136" t="n"/>
+      <c r="F56" s="136" t="n"/>
+      <c r="G56" s="136" t="n"/>
+      <c r="H56" s="137" t="n"/>
+      <c r="I56" s="137" t="n"/>
+      <c r="J56" s="135" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="33" t="n"/>
-      <c r="B57" s="33" t="n"/>
-      <c r="C57" s="33" t="n"/>
-      <c r="D57" s="33" t="n"/>
-      <c r="E57" s="112" t="n"/>
-      <c r="F57" s="112" t="n"/>
-      <c r="G57" s="112" t="n"/>
-      <c r="H57" s="113" t="n"/>
-      <c r="I57" s="113" t="n"/>
-      <c r="J57" s="33" t="n"/>
+      <c r="A57" s="138" t="n"/>
+      <c r="B57" s="138" t="n"/>
+      <c r="C57" s="138" t="n"/>
+      <c r="D57" s="138" t="n"/>
+      <c r="E57" s="139" t="n"/>
+      <c r="F57" s="139" t="n"/>
+      <c r="G57" s="139" t="n"/>
+      <c r="H57" s="140" t="n"/>
+      <c r="I57" s="140" t="n"/>
+      <c r="J57" s="138" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="n"/>
-      <c r="B58" s="32" t="n"/>
-      <c r="C58" s="32" t="n"/>
-      <c r="D58" s="32" t="n"/>
-      <c r="E58" s="110" t="n"/>
-      <c r="F58" s="110" t="n"/>
-      <c r="G58" s="110" t="n"/>
-      <c r="H58" s="111" t="n"/>
-      <c r="I58" s="111" t="n"/>
-      <c r="J58" s="32" t="n"/>
+      <c r="A58" s="135" t="n"/>
+      <c r="B58" s="135" t="n"/>
+      <c r="C58" s="135" t="n"/>
+      <c r="D58" s="135" t="n"/>
+      <c r="E58" s="136" t="n"/>
+      <c r="F58" s="136" t="n"/>
+      <c r="G58" s="136" t="n"/>
+      <c r="H58" s="137" t="n"/>
+      <c r="I58" s="137" t="n"/>
+      <c r="J58" s="135" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="33" t="n"/>
-      <c r="B59" s="33" t="n"/>
-      <c r="C59" s="33" t="n"/>
-      <c r="D59" s="33" t="n"/>
-      <c r="E59" s="112" t="n"/>
-      <c r="F59" s="112" t="n"/>
-      <c r="G59" s="112" t="n"/>
-      <c r="H59" s="113" t="n"/>
-      <c r="I59" s="113" t="n"/>
-      <c r="J59" s="33" t="n"/>
+      <c r="A59" s="138" t="n"/>
+      <c r="B59" s="138" t="n"/>
+      <c r="C59" s="138" t="n"/>
+      <c r="D59" s="138" t="n"/>
+      <c r="E59" s="139" t="n"/>
+      <c r="F59" s="139" t="n"/>
+      <c r="G59" s="139" t="n"/>
+      <c r="H59" s="140" t="n"/>
+      <c r="I59" s="140" t="n"/>
+      <c r="J59" s="138" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="n"/>
-      <c r="B60" s="32" t="n"/>
-      <c r="C60" s="32" t="n"/>
-      <c r="D60" s="32" t="n"/>
-      <c r="E60" s="110" t="n"/>
-      <c r="F60" s="110" t="n"/>
-      <c r="G60" s="110" t="n"/>
-      <c r="H60" s="111" t="n"/>
-      <c r="I60" s="111" t="n"/>
-      <c r="J60" s="32" t="n"/>
+      <c r="A60" s="135" t="n"/>
+      <c r="B60" s="135" t="n"/>
+      <c r="C60" s="135" t="n"/>
+      <c r="D60" s="135" t="n"/>
+      <c r="E60" s="136" t="n"/>
+      <c r="F60" s="136" t="n"/>
+      <c r="G60" s="136" t="n"/>
+      <c r="H60" s="137" t="n"/>
+      <c r="I60" s="137" t="n"/>
+      <c r="J60" s="135" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="33" t="n"/>
-      <c r="B61" s="33" t="n"/>
-      <c r="C61" s="33" t="n"/>
-      <c r="D61" s="33" t="n"/>
-      <c r="E61" s="112" t="n"/>
-      <c r="F61" s="112" t="n"/>
-      <c r="G61" s="112" t="n"/>
-      <c r="H61" s="113" t="n"/>
-      <c r="I61" s="113" t="n"/>
-      <c r="J61" s="33" t="n"/>
+      <c r="A61" s="138" t="n"/>
+      <c r="B61" s="138" t="n"/>
+      <c r="C61" s="138" t="n"/>
+      <c r="D61" s="138" t="n"/>
+      <c r="E61" s="139" t="n"/>
+      <c r="F61" s="139" t="n"/>
+      <c r="G61" s="139" t="n"/>
+      <c r="H61" s="140" t="n"/>
+      <c r="I61" s="140" t="n"/>
+      <c r="J61" s="138" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="32" t="n"/>
-      <c r="B62" s="32" t="n"/>
-      <c r="C62" s="32" t="n"/>
-      <c r="D62" s="32" t="n"/>
-      <c r="E62" s="110" t="n"/>
-      <c r="F62" s="110" t="n"/>
-      <c r="G62" s="110" t="n"/>
-      <c r="H62" s="111" t="n"/>
-      <c r="I62" s="111" t="n"/>
-      <c r="J62" s="32" t="n"/>
+      <c r="A62" s="135" t="n"/>
+      <c r="B62" s="135" t="n"/>
+      <c r="C62" s="135" t="n"/>
+      <c r="D62" s="135" t="n"/>
+      <c r="E62" s="136" t="n"/>
+      <c r="F62" s="136" t="n"/>
+      <c r="G62" s="136" t="n"/>
+      <c r="H62" s="137" t="n"/>
+      <c r="I62" s="137" t="n"/>
+      <c r="J62" s="135" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="33" t="n"/>
-      <c r="B63" s="33" t="n"/>
-      <c r="C63" s="33" t="n"/>
-      <c r="D63" s="33" t="n"/>
-      <c r="E63" s="112" t="n"/>
-      <c r="F63" s="112" t="n"/>
-      <c r="G63" s="112" t="n"/>
-      <c r="H63" s="113" t="n"/>
-      <c r="I63" s="113" t="n"/>
-      <c r="J63" s="33" t="n"/>
+      <c r="A63" s="138" t="n"/>
+      <c r="B63" s="138" t="n"/>
+      <c r="C63" s="138" t="n"/>
+      <c r="D63" s="138" t="n"/>
+      <c r="E63" s="139" t="n"/>
+      <c r="F63" s="139" t="n"/>
+      <c r="G63" s="139" t="n"/>
+      <c r="H63" s="140" t="n"/>
+      <c r="I63" s="140" t="n"/>
+      <c r="J63" s="138" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="32" t="n"/>
-      <c r="B64" s="32" t="n"/>
-      <c r="C64" s="32" t="n"/>
-      <c r="D64" s="32" t="n"/>
-      <c r="E64" s="110" t="n"/>
-      <c r="F64" s="110" t="n"/>
-      <c r="G64" s="110" t="n"/>
-      <c r="H64" s="111" t="n"/>
-      <c r="I64" s="111" t="n"/>
-      <c r="J64" s="32" t="n"/>
+      <c r="A64" s="135" t="n"/>
+      <c r="B64" s="135" t="n"/>
+      <c r="C64" s="135" t="n"/>
+      <c r="D64" s="135" t="n"/>
+      <c r="E64" s="136" t="n"/>
+      <c r="F64" s="136" t="n"/>
+      <c r="G64" s="136" t="n"/>
+      <c r="H64" s="137" t="n"/>
+      <c r="I64" s="137" t="n"/>
+      <c r="J64" s="135" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="33" t="n"/>
-      <c r="B65" s="33" t="n"/>
-      <c r="C65" s="33" t="n"/>
-      <c r="D65" s="33" t="n"/>
-      <c r="E65" s="112" t="n"/>
-      <c r="F65" s="112" t="n"/>
-      <c r="G65" s="112" t="n"/>
-      <c r="H65" s="113" t="n"/>
-      <c r="I65" s="113" t="n"/>
-      <c r="J65" s="33" t="n"/>
+      <c r="A65" s="138" t="n"/>
+      <c r="B65" s="138" t="n"/>
+      <c r="C65" s="138" t="n"/>
+      <c r="D65" s="138" t="n"/>
+      <c r="E65" s="139" t="n"/>
+      <c r="F65" s="139" t="n"/>
+      <c r="G65" s="139" t="n"/>
+      <c r="H65" s="140" t="n"/>
+      <c r="I65" s="140" t="n"/>
+      <c r="J65" s="138" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="32" t="n"/>
-      <c r="B66" s="32" t="n"/>
-      <c r="C66" s="32" t="n"/>
-      <c r="D66" s="32" t="n"/>
-      <c r="E66" s="110" t="n"/>
-      <c r="F66" s="110" t="n"/>
-      <c r="G66" s="110" t="n"/>
-      <c r="H66" s="111" t="n"/>
-      <c r="I66" s="111" t="n"/>
-      <c r="J66" s="32" t="n"/>
+      <c r="A66" s="135" t="n"/>
+      <c r="B66" s="135" t="n"/>
+      <c r="C66" s="135" t="n"/>
+      <c r="D66" s="135" t="n"/>
+      <c r="E66" s="136" t="n"/>
+      <c r="F66" s="136" t="n"/>
+      <c r="G66" s="136" t="n"/>
+      <c r="H66" s="137" t="n"/>
+      <c r="I66" s="137" t="n"/>
+      <c r="J66" s="135" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="33" t="n"/>
-      <c r="B67" s="33" t="n"/>
-      <c r="C67" s="33" t="n"/>
-      <c r="D67" s="33" t="n"/>
-      <c r="E67" s="112" t="n"/>
-      <c r="F67" s="112" t="n"/>
-      <c r="G67" s="112" t="n"/>
-      <c r="H67" s="113" t="n"/>
-      <c r="I67" s="113" t="n"/>
-      <c r="J67" s="33" t="n"/>
+      <c r="A67" s="138" t="n"/>
+      <c r="B67" s="138" t="n"/>
+      <c r="C67" s="138" t="n"/>
+      <c r="D67" s="138" t="n"/>
+      <c r="E67" s="139" t="n"/>
+      <c r="F67" s="139" t="n"/>
+      <c r="G67" s="139" t="n"/>
+      <c r="H67" s="140" t="n"/>
+      <c r="I67" s="140" t="n"/>
+      <c r="J67" s="138" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="32" t="n"/>
-      <c r="B68" s="32" t="n"/>
-      <c r="C68" s="32" t="n"/>
-      <c r="D68" s="32" t="n"/>
-      <c r="E68" s="110" t="n"/>
-      <c r="F68" s="110" t="n"/>
-      <c r="G68" s="110" t="n"/>
-      <c r="H68" s="111" t="n"/>
-      <c r="I68" s="111" t="n"/>
-      <c r="J68" s="32" t="n"/>
+      <c r="A68" s="135" t="n"/>
+      <c r="B68" s="135" t="n"/>
+      <c r="C68" s="135" t="n"/>
+      <c r="D68" s="135" t="n"/>
+      <c r="E68" s="136" t="n"/>
+      <c r="F68" s="136" t="n"/>
+      <c r="G68" s="136" t="n"/>
+      <c r="H68" s="137" t="n"/>
+      <c r="I68" s="137" t="n"/>
+      <c r="J68" s="135" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="33" t="n"/>
-      <c r="B69" s="33" t="n"/>
-      <c r="C69" s="33" t="n"/>
-      <c r="D69" s="33" t="n"/>
-      <c r="E69" s="112" t="n"/>
-      <c r="F69" s="112" t="n"/>
-      <c r="G69" s="112" t="n"/>
-      <c r="H69" s="113" t="n"/>
-      <c r="I69" s="113" t="n"/>
-      <c r="J69" s="33" t="n"/>
+      <c r="A69" s="138" t="n"/>
+      <c r="B69" s="138" t="n"/>
+      <c r="C69" s="138" t="n"/>
+      <c r="D69" s="138" t="n"/>
+      <c r="E69" s="139" t="n"/>
+      <c r="F69" s="139" t="n"/>
+      <c r="G69" s="139" t="n"/>
+      <c r="H69" s="140" t="n"/>
+      <c r="I69" s="140" t="n"/>
+      <c r="J69" s="138" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="32" t="n"/>
-      <c r="B70" s="32" t="n"/>
-      <c r="C70" s="32" t="n"/>
-      <c r="D70" s="32" t="n"/>
-      <c r="E70" s="110" t="n"/>
-      <c r="F70" s="110" t="n"/>
-      <c r="G70" s="110" t="n"/>
-      <c r="H70" s="111" t="n"/>
-      <c r="I70" s="111" t="n"/>
-      <c r="J70" s="32" t="n"/>
+      <c r="A70" s="135" t="n"/>
+      <c r="B70" s="135" t="n"/>
+      <c r="C70" s="135" t="n"/>
+      <c r="D70" s="135" t="n"/>
+      <c r="E70" s="136" t="n"/>
+      <c r="F70" s="136" t="n"/>
+      <c r="G70" s="136" t="n"/>
+      <c r="H70" s="137" t="n"/>
+      <c r="I70" s="137" t="n"/>
+      <c r="J70" s="135" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="33" t="n"/>
-      <c r="B71" s="33" t="n"/>
-      <c r="C71" s="33" t="n"/>
-      <c r="D71" s="33" t="n"/>
-      <c r="E71" s="112" t="n"/>
-      <c r="F71" s="112" t="n"/>
-      <c r="G71" s="112" t="n"/>
-      <c r="H71" s="113" t="n"/>
-      <c r="I71" s="113" t="n"/>
-      <c r="J71" s="33" t="n"/>
+      <c r="A71" s="138" t="n"/>
+      <c r="B71" s="138" t="n"/>
+      <c r="C71" s="138" t="n"/>
+      <c r="D71" s="138" t="n"/>
+      <c r="E71" s="139" t="n"/>
+      <c r="F71" s="139" t="n"/>
+      <c r="G71" s="139" t="n"/>
+      <c r="H71" s="140" t="n"/>
+      <c r="I71" s="140" t="n"/>
+      <c r="J71" s="138" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="32" t="n"/>
-      <c r="B72" s="32" t="n"/>
-      <c r="C72" s="32" t="n"/>
-      <c r="D72" s="32" t="n"/>
-      <c r="E72" s="110" t="n"/>
-      <c r="F72" s="110" t="n"/>
-      <c r="G72" s="110" t="n"/>
-      <c r="H72" s="111" t="n"/>
-      <c r="I72" s="111" t="n"/>
-      <c r="J72" s="32" t="n"/>
+      <c r="A72" s="135" t="n"/>
+      <c r="B72" s="135" t="n"/>
+      <c r="C72" s="135" t="n"/>
+      <c r="D72" s="135" t="n"/>
+      <c r="E72" s="136" t="n"/>
+      <c r="F72" s="136" t="n"/>
+      <c r="G72" s="136" t="n"/>
+      <c r="H72" s="137" t="n"/>
+      <c r="I72" s="137" t="n"/>
+      <c r="J72" s="135" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="33" t="n"/>
-      <c r="B73" s="33" t="n"/>
-      <c r="C73" s="33" t="n"/>
-      <c r="D73" s="33" t="n"/>
-      <c r="E73" s="112" t="n"/>
-      <c r="F73" s="112" t="n"/>
-      <c r="G73" s="112" t="n"/>
-      <c r="H73" s="113" t="n"/>
-      <c r="I73" s="113" t="n"/>
-      <c r="J73" s="33" t="n"/>
+      <c r="A73" s="138" t="n"/>
+      <c r="B73" s="138" t="n"/>
+      <c r="C73" s="138" t="n"/>
+      <c r="D73" s="138" t="n"/>
+      <c r="E73" s="139" t="n"/>
+      <c r="F73" s="139" t="n"/>
+      <c r="G73" s="139" t="n"/>
+      <c r="H73" s="140" t="n"/>
+      <c r="I73" s="140" t="n"/>
+      <c r="J73" s="138" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="32" t="n"/>
-      <c r="B74" s="32" t="n"/>
-      <c r="C74" s="32" t="n"/>
-      <c r="D74" s="32" t="n"/>
-      <c r="E74" s="110" t="n"/>
-      <c r="F74" s="110" t="n"/>
-      <c r="G74" s="110" t="n"/>
-      <c r="H74" s="111" t="n"/>
-      <c r="I74" s="111" t="n"/>
-      <c r="J74" s="32" t="n"/>
+      <c r="A74" s="135" t="n"/>
+      <c r="B74" s="135" t="n"/>
+      <c r="C74" s="135" t="n"/>
+      <c r="D74" s="135" t="n"/>
+      <c r="E74" s="136" t="n"/>
+      <c r="F74" s="136" t="n"/>
+      <c r="G74" s="136" t="n"/>
+      <c r="H74" s="137" t="n"/>
+      <c r="I74" s="137" t="n"/>
+      <c r="J74" s="135" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="33" t="n"/>
-      <c r="B75" s="33" t="n"/>
-      <c r="C75" s="33" t="n"/>
-      <c r="D75" s="33" t="n"/>
-      <c r="E75" s="112" t="n"/>
-      <c r="F75" s="112" t="n"/>
-      <c r="G75" s="112" t="n"/>
-      <c r="H75" s="113" t="n"/>
-      <c r="I75" s="113" t="n"/>
-      <c r="J75" s="33" t="n"/>
+      <c r="A75" s="138" t="n"/>
+      <c r="B75" s="138" t="n"/>
+      <c r="C75" s="138" t="n"/>
+      <c r="D75" s="138" t="n"/>
+      <c r="E75" s="139" t="n"/>
+      <c r="F75" s="139" t="n"/>
+      <c r="G75" s="139" t="n"/>
+      <c r="H75" s="140" t="n"/>
+      <c r="I75" s="140" t="n"/>
+      <c r="J75" s="138" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="32" t="n"/>
-      <c r="B76" s="32" t="n"/>
-      <c r="C76" s="32" t="n"/>
-      <c r="D76" s="32" t="n"/>
-      <c r="E76" s="110" t="n"/>
-      <c r="F76" s="110" t="n"/>
-      <c r="G76" s="110" t="n"/>
-      <c r="H76" s="111" t="n"/>
-      <c r="I76" s="111" t="n"/>
-      <c r="J76" s="32" t="n"/>
+      <c r="A76" s="135" t="n"/>
+      <c r="B76" s="135" t="n"/>
+      <c r="C76" s="135" t="n"/>
+      <c r="D76" s="135" t="n"/>
+      <c r="E76" s="136" t="n"/>
+      <c r="F76" s="136" t="n"/>
+      <c r="G76" s="136" t="n"/>
+      <c r="H76" s="137" t="n"/>
+      <c r="I76" s="137" t="n"/>
+      <c r="J76" s="135" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="33" t="n"/>
-      <c r="B77" s="33" t="n"/>
-      <c r="C77" s="33" t="n"/>
-      <c r="D77" s="33" t="n"/>
-      <c r="E77" s="112" t="n"/>
-      <c r="F77" s="112" t="n"/>
-      <c r="G77" s="112" t="n"/>
-      <c r="H77" s="113" t="n"/>
-      <c r="I77" s="113" t="n"/>
-      <c r="J77" s="33" t="n"/>
+      <c r="A77" s="138" t="n"/>
+      <c r="B77" s="138" t="n"/>
+      <c r="C77" s="138" t="n"/>
+      <c r="D77" s="138" t="n"/>
+      <c r="E77" s="139" t="n"/>
+      <c r="F77" s="139" t="n"/>
+      <c r="G77" s="139" t="n"/>
+      <c r="H77" s="140" t="n"/>
+      <c r="I77" s="140" t="n"/>
+      <c r="J77" s="138" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="32" t="n"/>
-      <c r="B78" s="32" t="n"/>
-      <c r="C78" s="32" t="n"/>
-      <c r="D78" s="32" t="n"/>
-      <c r="E78" s="110" t="n"/>
-      <c r="F78" s="110" t="n"/>
-      <c r="G78" s="110" t="n"/>
-      <c r="H78" s="111" t="n"/>
-      <c r="I78" s="111" t="n"/>
-      <c r="J78" s="32" t="n"/>
+      <c r="A78" s="135" t="n"/>
+      <c r="B78" s="135" t="n"/>
+      <c r="C78" s="135" t="n"/>
+      <c r="D78" s="135" t="n"/>
+      <c r="E78" s="136" t="n"/>
+      <c r="F78" s="136" t="n"/>
+      <c r="G78" s="136" t="n"/>
+      <c r="H78" s="137" t="n"/>
+      <c r="I78" s="137" t="n"/>
+      <c r="J78" s="135" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="33" t="n"/>
-      <c r="B79" s="33" t="n"/>
-      <c r="C79" s="33" t="n"/>
-      <c r="D79" s="33" t="n"/>
-      <c r="E79" s="112" t="n"/>
-      <c r="F79" s="112" t="n"/>
-      <c r="G79" s="112" t="n"/>
-      <c r="H79" s="113" t="n"/>
-      <c r="I79" s="113" t="n"/>
-      <c r="J79" s="33" t="n"/>
+      <c r="A79" s="138" t="n"/>
+      <c r="B79" s="138" t="n"/>
+      <c r="C79" s="138" t="n"/>
+      <c r="D79" s="138" t="n"/>
+      <c r="E79" s="139" t="n"/>
+      <c r="F79" s="139" t="n"/>
+      <c r="G79" s="139" t="n"/>
+      <c r="H79" s="140" t="n"/>
+      <c r="I79" s="140" t="n"/>
+      <c r="J79" s="138" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="32" t="n"/>
-      <c r="B80" s="32" t="n"/>
-      <c r="C80" s="32" t="n"/>
-      <c r="D80" s="32" t="n"/>
-      <c r="E80" s="110" t="n"/>
-      <c r="F80" s="110" t="n"/>
-      <c r="G80" s="110" t="n"/>
-      <c r="H80" s="111" t="n"/>
-      <c r="I80" s="111" t="n"/>
-      <c r="J80" s="32" t="n"/>
+      <c r="A80" s="135" t="n"/>
+      <c r="B80" s="135" t="n"/>
+      <c r="C80" s="135" t="n"/>
+      <c r="D80" s="135" t="n"/>
+      <c r="E80" s="136" t="n"/>
+      <c r="F80" s="136" t="n"/>
+      <c r="G80" s="136" t="n"/>
+      <c r="H80" s="137" t="n"/>
+      <c r="I80" s="137" t="n"/>
+      <c r="J80" s="135" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="33" t="n"/>
-      <c r="B81" s="33" t="n"/>
-      <c r="C81" s="33" t="n"/>
-      <c r="D81" s="33" t="n"/>
-      <c r="E81" s="112" t="n"/>
-      <c r="F81" s="112" t="n"/>
-      <c r="G81" s="112" t="n"/>
-      <c r="H81" s="113" t="n"/>
-      <c r="I81" s="113" t="n"/>
-      <c r="J81" s="33" t="n"/>
+      <c r="A81" s="138" t="n"/>
+      <c r="B81" s="138" t="n"/>
+      <c r="C81" s="138" t="n"/>
+      <c r="D81" s="138" t="n"/>
+      <c r="E81" s="139" t="n"/>
+      <c r="F81" s="139" t="n"/>
+      <c r="G81" s="139" t="n"/>
+      <c r="H81" s="140" t="n"/>
+      <c r="I81" s="140" t="n"/>
+      <c r="J81" s="138" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="32" t="n"/>
-      <c r="B82" s="32" t="n"/>
-      <c r="C82" s="32" t="n"/>
-      <c r="D82" s="32" t="n"/>
-      <c r="E82" s="110" t="n"/>
-      <c r="F82" s="110" t="n"/>
-      <c r="G82" s="110" t="n"/>
-      <c r="H82" s="111" t="n"/>
-      <c r="I82" s="111" t="n"/>
-      <c r="J82" s="32" t="n"/>
+      <c r="A82" s="135" t="n"/>
+      <c r="B82" s="135" t="n"/>
+      <c r="C82" s="135" t="n"/>
+      <c r="D82" s="135" t="n"/>
+      <c r="E82" s="136" t="n"/>
+      <c r="F82" s="136" t="n"/>
+      <c r="G82" s="136" t="n"/>
+      <c r="H82" s="137" t="n"/>
+      <c r="I82" s="137" t="n"/>
+      <c r="J82" s="135" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="33" t="n"/>
-      <c r="B83" s="33" t="n"/>
-      <c r="C83" s="33" t="n"/>
-      <c r="D83" s="33" t="n"/>
-      <c r="E83" s="112" t="n"/>
-      <c r="F83" s="112" t="n"/>
-      <c r="G83" s="112" t="n"/>
-      <c r="H83" s="113" t="n"/>
-      <c r="I83" s="113" t="n"/>
-      <c r="J83" s="33" t="n"/>
+      <c r="A83" s="138" t="n"/>
+      <c r="B83" s="138" t="n"/>
+      <c r="C83" s="138" t="n"/>
+      <c r="D83" s="138" t="n"/>
+      <c r="E83" s="139" t="n"/>
+      <c r="F83" s="139" t="n"/>
+      <c r="G83" s="139" t="n"/>
+      <c r="H83" s="140" t="n"/>
+      <c r="I83" s="140" t="n"/>
+      <c r="J83" s="138" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="32" t="n"/>
-      <c r="B84" s="32" t="n"/>
-      <c r="C84" s="32" t="n"/>
-      <c r="D84" s="32" t="n"/>
-      <c r="E84" s="110" t="n"/>
-      <c r="F84" s="110" t="n"/>
-      <c r="G84" s="110" t="n"/>
-      <c r="H84" s="111" t="n"/>
-      <c r="I84" s="111" t="n"/>
-      <c r="J84" s="32" t="n"/>
+      <c r="A84" s="135" t="n"/>
+      <c r="B84" s="135" t="n"/>
+      <c r="C84" s="135" t="n"/>
+      <c r="D84" s="135" t="n"/>
+      <c r="E84" s="136" t="n"/>
+      <c r="F84" s="136" t="n"/>
+      <c r="G84" s="136" t="n"/>
+      <c r="H84" s="137" t="n"/>
+      <c r="I84" s="137" t="n"/>
+      <c r="J84" s="135" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="33" t="n"/>
-      <c r="B85" s="33" t="n"/>
-      <c r="C85" s="33" t="n"/>
-      <c r="D85" s="33" t="n"/>
-      <c r="E85" s="112" t="n"/>
-      <c r="F85" s="112" t="n"/>
-      <c r="G85" s="112" t="n"/>
-      <c r="H85" s="113" t="n"/>
-      <c r="I85" s="113" t="n"/>
-      <c r="J85" s="33" t="n"/>
+      <c r="A85" s="138" t="n"/>
+      <c r="B85" s="138" t="n"/>
+      <c r="C85" s="138" t="n"/>
+      <c r="D85" s="138" t="n"/>
+      <c r="E85" s="139" t="n"/>
+      <c r="F85" s="139" t="n"/>
+      <c r="G85" s="139" t="n"/>
+      <c r="H85" s="140" t="n"/>
+      <c r="I85" s="140" t="n"/>
+      <c r="J85" s="138" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="32" t="n"/>
-      <c r="B86" s="32" t="n"/>
-      <c r="C86" s="32" t="n"/>
-      <c r="D86" s="32" t="n"/>
-      <c r="E86" s="110" t="n"/>
-      <c r="F86" s="110" t="n"/>
-      <c r="G86" s="110" t="n"/>
-      <c r="H86" s="111" t="n"/>
-      <c r="I86" s="111" t="n"/>
-      <c r="J86" s="32" t="n"/>
+      <c r="A86" s="135" t="n"/>
+      <c r="B86" s="135" t="n"/>
+      <c r="C86" s="135" t="n"/>
+      <c r="D86" s="135" t="n"/>
+      <c r="E86" s="136" t="n"/>
+      <c r="F86" s="136" t="n"/>
+      <c r="G86" s="136" t="n"/>
+      <c r="H86" s="137" t="n"/>
+      <c r="I86" s="137" t="n"/>
+      <c r="J86" s="135" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="33" t="n"/>
-      <c r="B87" s="33" t="n"/>
-      <c r="C87" s="33" t="n"/>
-      <c r="D87" s="33" t="n"/>
-      <c r="E87" s="112" t="n"/>
-      <c r="F87" s="112" t="n"/>
-      <c r="G87" s="112" t="n"/>
-      <c r="H87" s="113" t="n"/>
-      <c r="I87" s="113" t="n"/>
-      <c r="J87" s="33" t="n"/>
+      <c r="A87" s="138" t="n"/>
+      <c r="B87" s="138" t="n"/>
+      <c r="C87" s="138" t="n"/>
+      <c r="D87" s="138" t="n"/>
+      <c r="E87" s="139" t="n"/>
+      <c r="F87" s="139" t="n"/>
+      <c r="G87" s="139" t="n"/>
+      <c r="H87" s="140" t="n"/>
+      <c r="I87" s="140" t="n"/>
+      <c r="J87" s="138" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="32" t="n"/>
-      <c r="B88" s="32" t="n"/>
-      <c r="C88" s="32" t="n"/>
-      <c r="D88" s="32" t="n"/>
-      <c r="E88" s="110" t="n"/>
-      <c r="F88" s="110" t="n"/>
-      <c r="G88" s="110" t="n"/>
-      <c r="H88" s="111" t="n"/>
-      <c r="I88" s="111" t="n"/>
-      <c r="J88" s="32" t="n"/>
+      <c r="A88" s="135" t="n"/>
+      <c r="B88" s="135" t="n"/>
+      <c r="C88" s="135" t="n"/>
+      <c r="D88" s="135" t="n"/>
+      <c r="E88" s="136" t="n"/>
+      <c r="F88" s="136" t="n"/>
+      <c r="G88" s="136" t="n"/>
+      <c r="H88" s="137" t="n"/>
+      <c r="I88" s="137" t="n"/>
+      <c r="J88" s="135" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="33" t="n"/>
-      <c r="B89" s="33" t="n"/>
-      <c r="C89" s="33" t="n"/>
-      <c r="D89" s="33" t="n"/>
-      <c r="E89" s="112" t="n"/>
-      <c r="F89" s="112" t="n"/>
-      <c r="G89" s="112" t="n"/>
-      <c r="H89" s="113" t="n"/>
-      <c r="I89" s="113" t="n"/>
-      <c r="J89" s="33" t="n"/>
+      <c r="A89" s="138" t="n"/>
+      <c r="B89" s="138" t="n"/>
+      <c r="C89" s="138" t="n"/>
+      <c r="D89" s="138" t="n"/>
+      <c r="E89" s="139" t="n"/>
+      <c r="F89" s="139" t="n"/>
+      <c r="G89" s="139" t="n"/>
+      <c r="H89" s="140" t="n"/>
+      <c r="I89" s="140" t="n"/>
+      <c r="J89" s="138" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="32" t="n"/>
-      <c r="B90" s="32" t="n"/>
-      <c r="C90" s="32" t="n"/>
-      <c r="D90" s="32" t="n"/>
-      <c r="E90" s="110" t="n"/>
-      <c r="F90" s="110" t="n"/>
-      <c r="G90" s="110" t="n"/>
-      <c r="H90" s="111" t="n"/>
-      <c r="I90" s="111" t="n"/>
-      <c r="J90" s="32" t="n"/>
+      <c r="A90" s="135" t="n"/>
+      <c r="B90" s="135" t="n"/>
+      <c r="C90" s="135" t="n"/>
+      <c r="D90" s="135" t="n"/>
+      <c r="E90" s="136" t="n"/>
+      <c r="F90" s="136" t="n"/>
+      <c r="G90" s="136" t="n"/>
+      <c r="H90" s="137" t="n"/>
+      <c r="I90" s="137" t="n"/>
+      <c r="J90" s="135" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="33" t="n"/>
-      <c r="B91" s="33" t="n"/>
-      <c r="C91" s="33" t="n"/>
-      <c r="D91" s="33" t="n"/>
-      <c r="E91" s="112" t="n"/>
-      <c r="F91" s="112" t="n"/>
-      <c r="G91" s="112" t="n"/>
-      <c r="H91" s="113" t="n"/>
-      <c r="I91" s="113" t="n"/>
-      <c r="J91" s="33" t="n"/>
+      <c r="A91" s="138" t="n"/>
+      <c r="B91" s="138" t="n"/>
+      <c r="C91" s="138" t="n"/>
+      <c r="D91" s="138" t="n"/>
+      <c r="E91" s="139" t="n"/>
+      <c r="F91" s="139" t="n"/>
+      <c r="G91" s="139" t="n"/>
+      <c r="H91" s="140" t="n"/>
+      <c r="I91" s="140" t="n"/>
+      <c r="J91" s="138" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="32" t="n"/>
-      <c r="B92" s="32" t="n"/>
-      <c r="C92" s="32" t="n"/>
-      <c r="D92" s="32" t="n"/>
-      <c r="E92" s="110" t="n"/>
-      <c r="F92" s="110" t="n"/>
-      <c r="G92" s="110" t="n"/>
-      <c r="H92" s="111" t="n"/>
-      <c r="I92" s="111" t="n"/>
-      <c r="J92" s="32" t="n"/>
+      <c r="A92" s="135" t="n"/>
+      <c r="B92" s="135" t="n"/>
+      <c r="C92" s="135" t="n"/>
+      <c r="D92" s="135" t="n"/>
+      <c r="E92" s="136" t="n"/>
+      <c r="F92" s="136" t="n"/>
+      <c r="G92" s="136" t="n"/>
+      <c r="H92" s="137" t="n"/>
+      <c r="I92" s="137" t="n"/>
+      <c r="J92" s="135" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="33" t="n"/>
-      <c r="B93" s="33" t="n"/>
-      <c r="C93" s="33" t="n"/>
-      <c r="D93" s="33" t="n"/>
-      <c r="E93" s="112" t="n"/>
-      <c r="F93" s="112" t="n"/>
-      <c r="G93" s="112" t="n"/>
-      <c r="H93" s="113" t="n"/>
-      <c r="I93" s="113" t="n"/>
-      <c r="J93" s="33" t="n"/>
+      <c r="A93" s="138" t="n"/>
+      <c r="B93" s="138" t="n"/>
+      <c r="C93" s="138" t="n"/>
+      <c r="D93" s="138" t="n"/>
+      <c r="E93" s="139" t="n"/>
+      <c r="F93" s="139" t="n"/>
+      <c r="G93" s="139" t="n"/>
+      <c r="H93" s="140" t="n"/>
+      <c r="I93" s="140" t="n"/>
+      <c r="J93" s="138" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="32" t="n"/>
-      <c r="B94" s="32" t="n"/>
-      <c r="C94" s="32" t="n"/>
-      <c r="D94" s="32" t="n"/>
-      <c r="E94" s="110" t="n"/>
-      <c r="F94" s="110" t="n"/>
-      <c r="G94" s="110" t="n"/>
-      <c r="H94" s="111" t="n"/>
-      <c r="I94" s="111" t="n"/>
-      <c r="J94" s="32" t="n"/>
+      <c r="A94" s="135" t="n"/>
+      <c r="B94" s="135" t="n"/>
+      <c r="C94" s="135" t="n"/>
+      <c r="D94" s="135" t="n"/>
+      <c r="E94" s="136" t="n"/>
+      <c r="F94" s="136" t="n"/>
+      <c r="G94" s="136" t="n"/>
+      <c r="H94" s="137" t="n"/>
+      <c r="I94" s="137" t="n"/>
+      <c r="J94" s="135" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="33" t="n"/>
-      <c r="B95" s="33" t="n"/>
-      <c r="C95" s="33" t="n"/>
-      <c r="D95" s="33" t="n"/>
-      <c r="E95" s="112" t="n"/>
-      <c r="F95" s="112" t="n"/>
-      <c r="G95" s="112" t="n"/>
-      <c r="H95" s="113" t="n"/>
-      <c r="I95" s="113" t="n"/>
-      <c r="J95" s="33" t="n"/>
+      <c r="A95" s="138" t="n"/>
+      <c r="B95" s="138" t="n"/>
+      <c r="C95" s="138" t="n"/>
+      <c r="D95" s="138" t="n"/>
+      <c r="E95" s="139" t="n"/>
+      <c r="F95" s="139" t="n"/>
+      <c r="G95" s="139" t="n"/>
+      <c r="H95" s="140" t="n"/>
+      <c r="I95" s="140" t="n"/>
+      <c r="J95" s="138" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="32" t="n"/>
-      <c r="B96" s="32" t="n"/>
-      <c r="C96" s="32" t="n"/>
-      <c r="D96" s="32" t="n"/>
-      <c r="E96" s="110" t="n"/>
-      <c r="F96" s="110" t="n"/>
-      <c r="G96" s="110" t="n"/>
-      <c r="H96" s="111" t="n"/>
-      <c r="I96" s="111" t="n"/>
-      <c r="J96" s="32" t="n"/>
+      <c r="A96" s="135" t="n"/>
+      <c r="B96" s="135" t="n"/>
+      <c r="C96" s="135" t="n"/>
+      <c r="D96" s="135" t="n"/>
+      <c r="E96" s="136" t="n"/>
+      <c r="F96" s="136" t="n"/>
+      <c r="G96" s="136" t="n"/>
+      <c r="H96" s="137" t="n"/>
+      <c r="I96" s="137" t="n"/>
+      <c r="J96" s="135" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="33" t="n"/>
-      <c r="B97" s="33" t="n"/>
-      <c r="C97" s="33" t="n"/>
-      <c r="D97" s="33" t="n"/>
-      <c r="E97" s="112" t="n"/>
-      <c r="F97" s="112" t="n"/>
-      <c r="G97" s="112" t="n"/>
-      <c r="H97" s="113" t="n"/>
-      <c r="I97" s="113" t="n"/>
-      <c r="J97" s="33" t="n"/>
+      <c r="A97" s="138" t="n"/>
+      <c r="B97" s="138" t="n"/>
+      <c r="C97" s="138" t="n"/>
+      <c r="D97" s="138" t="n"/>
+      <c r="E97" s="139" t="n"/>
+      <c r="F97" s="139" t="n"/>
+      <c r="G97" s="139" t="n"/>
+      <c r="H97" s="140" t="n"/>
+      <c r="I97" s="140" t="n"/>
+      <c r="J97" s="138" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="32" t="n"/>
-      <c r="B98" s="32" t="n"/>
-      <c r="C98" s="32" t="n"/>
-      <c r="D98" s="32" t="n"/>
-      <c r="E98" s="110" t="n"/>
-      <c r="F98" s="110" t="n"/>
-      <c r="G98" s="110" t="n"/>
-      <c r="H98" s="111" t="n"/>
-      <c r="I98" s="111" t="n"/>
-      <c r="J98" s="32" t="n"/>
+      <c r="A98" s="135" t="n"/>
+      <c r="B98" s="135" t="n"/>
+      <c r="C98" s="135" t="n"/>
+      <c r="D98" s="135" t="n"/>
+      <c r="E98" s="136" t="n"/>
+      <c r="F98" s="136" t="n"/>
+      <c r="G98" s="136" t="n"/>
+      <c r="H98" s="137" t="n"/>
+      <c r="I98" s="137" t="n"/>
+      <c r="J98" s="135" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="33" t="n"/>
-      <c r="B99" s="33" t="n"/>
-      <c r="C99" s="33" t="n"/>
-      <c r="D99" s="33" t="n"/>
-      <c r="E99" s="112" t="n"/>
-      <c r="F99" s="112" t="n"/>
-      <c r="G99" s="112" t="n"/>
-      <c r="H99" s="113" t="n"/>
-      <c r="I99" s="113" t="n"/>
-      <c r="J99" s="33" t="n"/>
+      <c r="A99" s="138" t="n"/>
+      <c r="B99" s="138" t="n"/>
+      <c r="C99" s="138" t="n"/>
+      <c r="D99" s="138" t="n"/>
+      <c r="E99" s="139" t="n"/>
+      <c r="F99" s="139" t="n"/>
+      <c r="G99" s="139" t="n"/>
+      <c r="H99" s="140" t="n"/>
+      <c r="I99" s="140" t="n"/>
+      <c r="J99" s="138" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="32" t="n"/>
-      <c r="B100" s="32" t="n"/>
-      <c r="C100" s="32" t="n"/>
-      <c r="D100" s="32" t="n"/>
-      <c r="E100" s="110" t="n"/>
-      <c r="F100" s="110" t="n"/>
-      <c r="G100" s="110" t="n"/>
-      <c r="H100" s="111" t="n"/>
-      <c r="I100" s="111" t="n"/>
-      <c r="J100" s="32" t="n"/>
+      <c r="A100" s="135" t="n"/>
+      <c r="B100" s="135" t="n"/>
+      <c r="C100" s="135" t="n"/>
+      <c r="D100" s="135" t="n"/>
+      <c r="E100" s="136" t="n"/>
+      <c r="F100" s="136" t="n"/>
+      <c r="G100" s="136" t="n"/>
+      <c r="H100" s="137" t="n"/>
+      <c r="I100" s="137" t="n"/>
+      <c r="J100" s="135" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="33" t="n"/>
-      <c r="B101" s="33" t="n"/>
-      <c r="C101" s="33" t="n"/>
-      <c r="D101" s="33" t="n"/>
-      <c r="E101" s="112" t="n"/>
-      <c r="F101" s="112" t="n"/>
-      <c r="G101" s="112" t="n"/>
-      <c r="H101" s="113" t="n"/>
-      <c r="I101" s="113" t="n"/>
-      <c r="J101" s="33" t="n"/>
+      <c r="A101" s="138" t="n"/>
+      <c r="B101" s="138" t="n"/>
+      <c r="C101" s="138" t="n"/>
+      <c r="D101" s="138" t="n"/>
+      <c r="E101" s="139" t="n"/>
+      <c r="F101" s="139" t="n"/>
+      <c r="G101" s="139" t="n"/>
+      <c r="H101" s="140" t="n"/>
+      <c r="I101" s="140" t="n"/>
+      <c r="J101" s="138" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="32" t="n"/>
-      <c r="B102" s="32" t="n"/>
-      <c r="C102" s="32" t="n"/>
-      <c r="D102" s="32" t="n"/>
-      <c r="E102" s="110" t="n"/>
-      <c r="F102" s="110" t="n"/>
-      <c r="G102" s="110" t="n"/>
-      <c r="H102" s="111" t="n"/>
-      <c r="I102" s="111" t="n"/>
-      <c r="J102" s="32" t="n"/>
+      <c r="A102" s="135" t="n"/>
+      <c r="B102" s="135" t="n"/>
+      <c r="C102" s="135" t="n"/>
+      <c r="D102" s="135" t="n"/>
+      <c r="E102" s="136" t="n"/>
+      <c r="F102" s="136" t="n"/>
+      <c r="G102" s="136" t="n"/>
+      <c r="H102" s="137" t="n"/>
+      <c r="I102" s="137" t="n"/>
+      <c r="J102" s="135" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="34" t="n"/>
-      <c r="B103" s="34" t="n"/>
-      <c r="C103" s="34" t="n"/>
-      <c r="D103" s="34" t="n"/>
-      <c r="E103" s="114" t="n"/>
-      <c r="F103" s="114" t="n"/>
-      <c r="G103" s="114" t="n"/>
-      <c r="H103" s="115" t="n"/>
-      <c r="I103" s="115" t="n"/>
-      <c r="J103" s="34" t="n"/>
+      <c r="A103" s="141" t="n"/>
+      <c r="B103" s="141" t="n"/>
+      <c r="C103" s="141" t="n"/>
+      <c r="D103" s="141" t="n"/>
+      <c r="E103" s="142" t="n"/>
+      <c r="F103" s="142" t="n"/>
+      <c r="G103" s="142" t="n"/>
+      <c r="H103" s="143" t="n"/>
+      <c r="I103" s="143" t="n"/>
+      <c r="J103" s="141" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2785,7 +2933,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="85" t="inlineStr">
+      <c r="A1" s="144" t="inlineStr">
         <is>
           <t>MODE D’EMPLOI — ÉTAT DES CONGÉS PAR PERSONNE</t>
         </is>
@@ -2796,8 +2944,9 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="88" t="inlineStr">
+      <c r="A3" s="145" t="inlineStr">
         <is>
           <t>Objectif</t>
         </is>
@@ -2809,7 +2958,7 @@
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="88" t="inlineStr">
+      <c r="A4" s="145" t="inlineStr">
         <is>
           <t>Canevas</t>
         </is>
@@ -2821,7 +2970,7 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="88" t="inlineStr">
+      <c r="A5" s="145" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -2833,7 +2982,7 @@
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="88" t="inlineStr">
+      <c r="A6" s="145" t="inlineStr">
         <is>
           <t>Calcul métier</t>
         </is>
@@ -2845,7 +2994,7 @@
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="88" t="inlineStr">
+      <c r="A7" s="145" t="inlineStr">
         <is>
           <t>Totaux Excel</t>
         </is>
@@ -2857,7 +3006,7 @@
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="88" t="inlineStr">
+      <c r="A8" s="145" t="inlineStr">
         <is>
           <t>Période</t>
         </is>
@@ -2869,7 +3018,7 @@
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="88" t="inlineStr">
+      <c r="A9" s="145" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
@@ -2881,7 +3030,7 @@
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="88" t="inlineStr">
+      <c r="A10" s="145" t="inlineStr">
         <is>
           <t>Audit</t>
         </is>
